--- a/research/traditional_assets/database/data/canada/canada_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_real_estate_general_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06861936009579692</v>
+        <v>0.06847059379154304</v>
       </c>
       <c r="C2">
-        <v>727.6607864108628</v>
+        <v>721.3851978263193</v>
       </c>
       <c r="D2">
-        <v>718.3007864108628</v>
+        <v>720.2161978263193</v>
       </c>
       <c r="E2">
-        <v>-461.8999999999999</v>
+        <v>-453.7089999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="G2">
         <v>9.359999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>57.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4120072999999999</v>
       </c>
       <c r="N2">
-        <v>57.5</v>
+        <v>57.0879927</v>
       </c>
       <c r="O2">
-        <v>15.2375</v>
+        <v>15.1283180655</v>
       </c>
       <c r="P2">
-        <v>42.2625</v>
+        <v>41.9596746345</v>
       </c>
       <c r="Q2">
-        <v>51.2625</v>
+        <v>50.9596746345</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06861936009579692</v>
+        <v>0.06878877655711418</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313375</v>
+        <v>0.5309186271850852</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>139.5606339984753</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06847059379154304</v>
+        <v>0.06832182748728918</v>
       </c>
       <c r="C3">
-        <v>721.3851978263193</v>
+        <v>715.1198517760835</v>
       </c>
       <c r="D3">
-        <v>720.2161978263193</v>
+        <v>722.1418517760834</v>
       </c>
       <c r="E3">
-        <v>-453.7089999999999</v>
+        <v>-445.5179999999999</v>
       </c>
       <c r="F3">
-        <v>8.190999999999999</v>
+        <v>16.382</v>
       </c>
       <c r="G3">
         <v>9.359999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>57.5</v>
       </c>
       <c r="M3">
-        <v>0.4120072999999999</v>
+        <v>0.8240145999999998</v>
       </c>
       <c r="N3">
-        <v>57.0879927</v>
+        <v>56.6759854</v>
       </c>
       <c r="O3">
-        <v>15.1283180655</v>
+        <v>15.019136131</v>
       </c>
       <c r="P3">
-        <v>41.9596746345</v>
+        <v>41.656849269</v>
       </c>
       <c r="Q3">
-        <v>50.9596746345</v>
+        <v>50.656849269</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06878877655711418</v>
+        <v>0.06896165049723386</v>
       </c>
       <c r="T3">
-        <v>0.5309186271850852</v>
+        <v>0.5349110969338075</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>139.5606339984753</v>
+        <v>69.78031699923766</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06832182748728918</v>
+        <v>0.06817306118303532</v>
       </c>
       <c r="C4">
-        <v>715.1198517760835</v>
+        <v>708.864830637308</v>
       </c>
       <c r="D4">
-        <v>722.1418517760834</v>
+        <v>724.077830637308</v>
       </c>
       <c r="E4">
-        <v>-445.5179999999999</v>
+        <v>-437.3269999999999</v>
       </c>
       <c r="F4">
-        <v>16.382</v>
+        <v>24.573</v>
       </c>
       <c r="G4">
         <v>9.359999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>57.5</v>
       </c>
       <c r="M4">
-        <v>0.8240145999999998</v>
+        <v>1.2360219</v>
       </c>
       <c r="N4">
-        <v>56.6759854</v>
+        <v>56.2639781</v>
       </c>
       <c r="O4">
-        <v>15.019136131</v>
+        <v>14.9099541965</v>
       </c>
       <c r="P4">
-        <v>41.656849269</v>
+        <v>41.3540239035</v>
       </c>
       <c r="Q4">
-        <v>50.656849269</v>
+        <v>50.3540239035</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06896165049723386</v>
+        <v>0.06913808884849003</v>
       </c>
       <c r="T4">
-        <v>0.5349110969338075</v>
+        <v>0.538985885646421</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.78031699923766</v>
+        <v>46.52021133282511</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06817306118303532</v>
+        <v>0.06802429487878148</v>
       </c>
       <c r="C5">
-        <v>708.864830637308</v>
+        <v>702.6202176728949</v>
       </c>
       <c r="D5">
-        <v>724.077830637308</v>
+        <v>726.0242176728949</v>
       </c>
       <c r="E5">
-        <v>-437.3269999999999</v>
+        <v>-429.1359999999999</v>
       </c>
       <c r="F5">
-        <v>24.573</v>
+        <v>32.764</v>
       </c>
       <c r="G5">
         <v>9.359999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>57.5</v>
       </c>
       <c r="M5">
-        <v>1.2360219</v>
+        <v>1.6480292</v>
       </c>
       <c r="N5">
-        <v>56.2639781</v>
+        <v>55.8519708</v>
       </c>
       <c r="O5">
-        <v>14.9099541965</v>
+        <v>14.800772262</v>
       </c>
       <c r="P5">
-        <v>41.3540239035</v>
+        <v>41.051198538</v>
       </c>
       <c r="Q5">
-        <v>50.3540239035</v>
+        <v>50.051198538</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06913808884849003</v>
+        <v>0.0693182029987307</v>
       </c>
       <c r="T5">
-        <v>0.538985885646421</v>
+        <v>0.5431455657905472</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.52021133282511</v>
+        <v>34.89015849961883</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06802429487878148</v>
+        <v>0.06787552857452761</v>
       </c>
       <c r="C6">
-        <v>702.6202176728949</v>
+        <v>696.3860970434326</v>
       </c>
       <c r="D6">
-        <v>726.0242176728949</v>
+        <v>727.9810970434327</v>
       </c>
       <c r="E6">
-        <v>-429.1359999999999</v>
+        <v>-420.9449999999999</v>
       </c>
       <c r="F6">
-        <v>32.764</v>
+        <v>40.955</v>
       </c>
       <c r="G6">
         <v>9.359999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>57.5</v>
       </c>
       <c r="M6">
-        <v>1.6480292</v>
+        <v>2.0600365</v>
       </c>
       <c r="N6">
-        <v>55.8519708</v>
+        <v>55.4399635</v>
       </c>
       <c r="O6">
-        <v>14.800772262</v>
+        <v>14.6915903275</v>
       </c>
       <c r="P6">
-        <v>41.051198538</v>
+        <v>40.7483731725</v>
       </c>
       <c r="Q6">
-        <v>50.051198538</v>
+        <v>49.7483731725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0693182029987307</v>
+        <v>0.06950210902581853</v>
       </c>
       <c r="T6">
-        <v>0.5431455657905472</v>
+        <v>0.547392818148234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.89015849961883</v>
+        <v>27.91212679969506</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06787552857452761</v>
+        <v>0.06772676227027374</v>
       </c>
       <c r="C7">
-        <v>696.3860970434326</v>
+        <v>690.1625538193257</v>
       </c>
       <c r="D7">
-        <v>727.9810970434327</v>
+        <v>729.9485538193256</v>
       </c>
       <c r="E7">
-        <v>-420.9449999999999</v>
+        <v>-412.7539999999999</v>
       </c>
       <c r="F7">
-        <v>40.955</v>
+        <v>49.146</v>
       </c>
       <c r="G7">
         <v>9.359999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>57.5</v>
       </c>
       <c r="M7">
-        <v>2.0600365</v>
+        <v>2.4720438</v>
       </c>
       <c r="N7">
-        <v>55.4399635</v>
+        <v>55.0279562</v>
       </c>
       <c r="O7">
-        <v>14.6915903275</v>
+        <v>14.582408393</v>
       </c>
       <c r="P7">
-        <v>40.7483731725</v>
+        <v>40.445547807</v>
       </c>
       <c r="Q7">
-        <v>49.7483731725</v>
+        <v>49.445547807</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06950210902581853</v>
+        <v>0.06968992794709973</v>
       </c>
       <c r="T7">
-        <v>0.547392818148234</v>
+        <v>0.551730437577361</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.91212679969506</v>
+        <v>23.26010566641255</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06772676227027374</v>
+        <v>0.06757799596601989</v>
       </c>
       <c r="C8">
-        <v>690.1625538193257</v>
+        <v>683.9496739931226</v>
       </c>
       <c r="D8">
-        <v>729.9485538193256</v>
+        <v>731.9266739931226</v>
       </c>
       <c r="E8">
-        <v>-412.7539999999999</v>
+        <v>-404.5629999999999</v>
       </c>
       <c r="F8">
-        <v>49.14599999999999</v>
+        <v>57.33699999999999</v>
       </c>
       <c r="G8">
         <v>9.359999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>57.5</v>
       </c>
       <c r="M8">
-        <v>2.472043799999999</v>
+        <v>2.884051099999999</v>
       </c>
       <c r="N8">
-        <v>55.0279562</v>
+        <v>54.6159489</v>
       </c>
       <c r="O8">
-        <v>14.582408393</v>
+        <v>14.4732264585</v>
       </c>
       <c r="P8">
-        <v>40.445547807</v>
+        <v>40.1427224415</v>
       </c>
       <c r="Q8">
-        <v>49.445547807</v>
+        <v>49.1427224415</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06968992794709973</v>
+        <v>0.06988178598496762</v>
       </c>
       <c r="T8">
-        <v>0.5517304375773608</v>
+        <v>0.5561613391447486</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.26010566641255</v>
+        <v>19.93723342835361</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06757799596601989</v>
+        <v>0.06742922966176602</v>
       </c>
       <c r="C9">
-        <v>683.9496739931226</v>
+        <v>677.7475444920458</v>
       </c>
       <c r="D9">
-        <v>731.9266739931226</v>
+        <v>733.9155444920458</v>
       </c>
       <c r="E9">
-        <v>-404.5629999999999</v>
+        <v>-396.372</v>
       </c>
       <c r="F9">
-        <v>57.337</v>
+        <v>65.52799999999999</v>
       </c>
       <c r="G9">
         <v>9.359999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>57.5</v>
       </c>
       <c r="M9">
-        <v>2.8840511</v>
+        <v>3.296058399999999</v>
       </c>
       <c r="N9">
-        <v>54.6159489</v>
+        <v>54.2039416</v>
       </c>
       <c r="O9">
-        <v>14.4732264585</v>
+        <v>14.364044524</v>
       </c>
       <c r="P9">
-        <v>40.1427224415</v>
+        <v>39.839897076</v>
       </c>
       <c r="Q9">
-        <v>49.1427224415</v>
+        <v>48.839897076</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06988178598496762</v>
+        <v>0.07007781484974568</v>
       </c>
       <c r="T9">
-        <v>0.5561613391447486</v>
+        <v>0.5606885646592534</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.93723342835361</v>
+        <v>17.44507924980941</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06742922966176602</v>
+        <v>0.06728046335751216</v>
       </c>
       <c r="C10">
-        <v>677.7475444920458</v>
+        <v>671.5562531907242</v>
       </c>
       <c r="D10">
-        <v>733.9155444920458</v>
+        <v>735.9152531907241</v>
       </c>
       <c r="E10">
-        <v>-396.372</v>
+        <v>-388.1809999999999</v>
       </c>
       <c r="F10">
-        <v>65.52799999999999</v>
+        <v>73.71899999999999</v>
       </c>
       <c r="G10">
         <v>9.359999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>57.5</v>
       </c>
       <c r="M10">
-        <v>3.296058399999999</v>
+        <v>3.7080657</v>
       </c>
       <c r="N10">
-        <v>54.2039416</v>
+        <v>53.7919343</v>
       </c>
       <c r="O10">
-        <v>14.364044524</v>
+        <v>14.2548625895</v>
       </c>
       <c r="P10">
-        <v>39.839897076</v>
+        <v>39.5370717105</v>
       </c>
       <c r="Q10">
-        <v>48.839897076</v>
+        <v>48.5370717105</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07007781484974568</v>
+        <v>0.07027815204122215</v>
       </c>
       <c r="T10">
-        <v>0.5606885646592534</v>
+        <v>0.5653152896356154</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.44507924980941</v>
+        <v>15.5067371109417</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06728046335751216</v>
+        <v>0.06713169705325829</v>
       </c>
       <c r="C11">
-        <v>671.5562531907242</v>
+        <v>665.3758889241352</v>
       </c>
       <c r="D11">
-        <v>735.9152531907241</v>
+        <v>737.9258889241352</v>
       </c>
       <c r="E11">
-        <v>-388.1809999999999</v>
+        <v>-379.99</v>
       </c>
       <c r="F11">
-        <v>73.71899999999999</v>
+        <v>81.90999999999998</v>
       </c>
       <c r="G11">
         <v>9.359999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>57.5</v>
       </c>
       <c r="M11">
-        <v>3.7080657</v>
+        <v>4.120072999999999</v>
       </c>
       <c r="N11">
-        <v>53.7919343</v>
+        <v>53.379927</v>
       </c>
       <c r="O11">
-        <v>14.2548625895</v>
+        <v>14.145680655</v>
       </c>
       <c r="P11">
-        <v>39.5370717105</v>
+        <v>39.234246345</v>
       </c>
       <c r="Q11">
-        <v>48.5370717105</v>
+        <v>48.234246345</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07027815204122215</v>
+        <v>0.070482941170287</v>
       </c>
       <c r="T11">
-        <v>0.5653152896356154</v>
+        <v>0.5700448307225633</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.5067371109417</v>
+        <v>13.95606339984753</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06713169705325829</v>
+        <v>0.06710420574900443</v>
       </c>
       <c r="C12">
-        <v>665.3758889241352</v>
+        <v>657.5576481794997</v>
       </c>
       <c r="D12">
-        <v>737.9258889241352</v>
+        <v>738.2986481794997</v>
       </c>
       <c r="E12">
-        <v>-379.9899999999999</v>
+        <v>-371.7989999999999</v>
       </c>
       <c r="F12">
-        <v>81.91</v>
+        <v>90.10099999999998</v>
       </c>
       <c r="G12">
         <v>9.359999999999999</v>
@@ -2271,45 +2271,45 @@
         <v>57.5</v>
       </c>
       <c r="M12">
-        <v>4.120073</v>
+        <v>4.667231799999999</v>
       </c>
       <c r="N12">
-        <v>53.379927</v>
+        <v>52.8327682</v>
       </c>
       <c r="O12">
-        <v>14.145680655</v>
+        <v>14.000683573</v>
       </c>
       <c r="P12">
-        <v>39.234246345</v>
+        <v>38.832084627</v>
       </c>
       <c r="Q12">
-        <v>48.234246345</v>
+        <v>47.832084627</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.070482941170287</v>
+        <v>0.07069233230225218</v>
       </c>
       <c r="T12">
-        <v>0.5700448307225633</v>
+        <v>0.5748806536316898</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.265</v>
       </c>
       <c r="W12">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.95606339984753</v>
+        <v>12.31993662710303</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06710420574900443</v>
+        <v>0.06696646444475057</v>
       </c>
       <c r="C13">
-        <v>657.5576481794997</v>
+        <v>651.2399906609735</v>
       </c>
       <c r="D13">
-        <v>738.2986481794997</v>
+        <v>740.1719906609735</v>
       </c>
       <c r="E13">
-        <v>-371.7989999999999</v>
+        <v>-363.6079999999999</v>
       </c>
       <c r="F13">
-        <v>90.10099999999998</v>
+        <v>98.29199999999999</v>
       </c>
       <c r="G13">
         <v>9.359999999999999</v>
@@ -2353,28 +2353,28 @@
         <v>57.5</v>
       </c>
       <c r="M13">
-        <v>4.667231799999999</v>
+        <v>5.091525599999999</v>
       </c>
       <c r="N13">
-        <v>52.8327682</v>
+        <v>52.4084744</v>
       </c>
       <c r="O13">
-        <v>14.000683573</v>
+        <v>13.888245716</v>
       </c>
       <c r="P13">
-        <v>38.832084627</v>
+        <v>38.520228684</v>
       </c>
       <c r="Q13">
-        <v>47.832084627</v>
+        <v>47.520228684</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07069233230225218</v>
+        <v>0.0709064823235802</v>
       </c>
       <c r="T13">
-        <v>0.5748806536316898</v>
+        <v>0.5798263816069328</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.31993662710303</v>
+        <v>11.29327524151111</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06696646444475057</v>
+        <v>0.0668287231404967</v>
       </c>
       <c r="C14">
-        <v>651.2399906609735</v>
+        <v>644.9318640806858</v>
       </c>
       <c r="D14">
-        <v>740.1719906609735</v>
+        <v>742.0548640806858</v>
       </c>
       <c r="E14">
-        <v>-363.6079999999999</v>
+        <v>-355.4169999999999</v>
       </c>
       <c r="F14">
-        <v>98.29199999999999</v>
+        <v>106.483</v>
       </c>
       <c r="G14">
         <v>9.359999999999999</v>
@@ -2435,28 +2435,28 @@
         <v>57.5</v>
       </c>
       <c r="M14">
-        <v>5.091525599999999</v>
+        <v>5.515819399999999</v>
       </c>
       <c r="N14">
-        <v>52.4084744</v>
+        <v>51.9841806</v>
       </c>
       <c r="O14">
-        <v>13.888245716</v>
+        <v>13.775807859</v>
       </c>
       <c r="P14">
-        <v>38.520228684</v>
+        <v>38.20837274100001</v>
       </c>
       <c r="Q14">
-        <v>47.520228684</v>
+        <v>47.20837274100001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0709064823235802</v>
+        <v>0.07112555533390426</v>
       </c>
       <c r="T14">
-        <v>0.5798263816069328</v>
+        <v>0.5848858044781584</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.29327524151111</v>
+        <v>10.42456176139487</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0668287231404967</v>
+        <v>0.06686591183624285</v>
       </c>
       <c r="C15">
-        <v>644.9318640806858</v>
+        <v>636.2315647843975</v>
       </c>
       <c r="D15">
-        <v>742.0548640806858</v>
+        <v>741.5455647843975</v>
       </c>
       <c r="E15">
-        <v>-355.4169999999999</v>
+        <v>-347.2259999999999</v>
       </c>
       <c r="F15">
-        <v>106.483</v>
+        <v>114.674</v>
       </c>
       <c r="G15">
         <v>9.359999999999999</v>
@@ -2517,45 +2517,45 @@
         <v>57.5</v>
       </c>
       <c r="M15">
-        <v>5.515819399999999</v>
+        <v>6.135058999999999</v>
       </c>
       <c r="N15">
-        <v>51.9841806</v>
+        <v>51.364941</v>
       </c>
       <c r="O15">
-        <v>13.775807859</v>
+        <v>13.611709365</v>
       </c>
       <c r="P15">
-        <v>38.20837274100001</v>
+        <v>37.753231635</v>
       </c>
       <c r="Q15">
-        <v>47.20837274100001</v>
+        <v>46.753231635</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07112555533390426</v>
+        <v>0.07134972306539866</v>
       </c>
       <c r="T15">
-        <v>0.5848858044781584</v>
+        <v>0.5900628883463894</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.265</v>
       </c>
       <c r="W15">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.42456176139487</v>
+        <v>9.372363004169969</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06686591183624285</v>
+        <v>0.06674066553198899</v>
       </c>
       <c r="C16">
-        <v>636.2315647843975</v>
+        <v>629.7586072764954</v>
       </c>
       <c r="D16">
-        <v>741.5455647843975</v>
+        <v>743.2636072764953</v>
       </c>
       <c r="E16">
-        <v>-347.2259999999999</v>
+        <v>-339.0349999999999</v>
       </c>
       <c r="F16">
-        <v>114.674</v>
+        <v>122.865</v>
       </c>
       <c r="G16">
         <v>9.359999999999999</v>
@@ -2599,28 +2599,28 @@
         <v>57.5</v>
       </c>
       <c r="M16">
-        <v>6.135058999999999</v>
+        <v>6.573277500000001</v>
       </c>
       <c r="N16">
-        <v>51.364941</v>
+        <v>50.9267225</v>
       </c>
       <c r="O16">
-        <v>13.611709365</v>
+        <v>13.4955814625</v>
       </c>
       <c r="P16">
-        <v>37.753231635</v>
+        <v>37.4311410375</v>
       </c>
       <c r="Q16">
-        <v>46.753231635</v>
+        <v>46.4311410375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07134972306539866</v>
+        <v>0.07157916533175175</v>
       </c>
       <c r="T16">
-        <v>0.5900628883463894</v>
+        <v>0.5953617859526962</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.372363004169969</v>
+        <v>8.74753880389197</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06674066553198899</v>
+        <v>0.06661541922773513</v>
       </c>
       <c r="C17">
-        <v>629.7586072764954</v>
+        <v>623.2936291149022</v>
       </c>
       <c r="D17">
-        <v>743.2636072764953</v>
+        <v>744.9896291149021</v>
       </c>
       <c r="E17">
-        <v>-339.035</v>
+        <v>-330.8439999999999</v>
       </c>
       <c r="F17">
-        <v>122.865</v>
+        <v>131.056</v>
       </c>
       <c r="G17">
         <v>9.359999999999999</v>
@@ -2681,28 +2681,28 @@
         <v>57.5</v>
       </c>
       <c r="M17">
-        <v>6.573277499999999</v>
+        <v>7.011495999999999</v>
       </c>
       <c r="N17">
-        <v>50.9267225</v>
+        <v>50.488504</v>
       </c>
       <c r="O17">
-        <v>13.4955814625</v>
+        <v>13.37945356</v>
       </c>
       <c r="P17">
-        <v>37.4311410375</v>
+        <v>37.10905044</v>
       </c>
       <c r="Q17">
-        <v>46.4311410375</v>
+        <v>46.10905044</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07157916533175175</v>
+        <v>0.07181407050920849</v>
       </c>
       <c r="T17">
-        <v>0.5953617859526962</v>
+        <v>0.6007868477877247</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.747538803891972</v>
+        <v>8.200817628648721</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06661541922773513</v>
+        <v>0.06649017292348126</v>
       </c>
       <c r="C18">
-        <v>623.2936291149022</v>
+        <v>616.8366860184094</v>
       </c>
       <c r="D18">
-        <v>744.9896291149021</v>
+        <v>746.7236860184094</v>
       </c>
       <c r="E18">
-        <v>-330.8439999999999</v>
+        <v>-322.6529999999999</v>
       </c>
       <c r="F18">
-        <v>131.056</v>
+        <v>139.247</v>
       </c>
       <c r="G18">
         <v>9.359999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>57.5</v>
       </c>
       <c r="M18">
-        <v>7.011495999999999</v>
+        <v>7.449714499999999</v>
       </c>
       <c r="N18">
-        <v>50.488504</v>
+        <v>50.0502855</v>
       </c>
       <c r="O18">
-        <v>13.37945356</v>
+        <v>13.2633256575</v>
       </c>
       <c r="P18">
-        <v>37.10905044</v>
+        <v>36.7869598425</v>
       </c>
       <c r="Q18">
-        <v>46.10905044</v>
+        <v>45.7869598425</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07181407050920849</v>
+        <v>0.07205463605238707</v>
       </c>
       <c r="T18">
-        <v>0.6007868477877247</v>
+        <v>0.6063426340043202</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.200817628648721</v>
+        <v>7.718416591669387</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06649017292348126</v>
+        <v>0.06647076661922741</v>
       </c>
       <c r="C19">
-        <v>616.8366860184094</v>
+        <v>608.915092239336</v>
       </c>
       <c r="D19">
-        <v>746.7236860184094</v>
+        <v>746.993092239336</v>
       </c>
       <c r="E19">
-        <v>-322.6529999999999</v>
+        <v>-314.4619999999999</v>
       </c>
       <c r="F19">
-        <v>139.247</v>
+        <v>147.438</v>
       </c>
       <c r="G19">
         <v>9.359999999999999</v>
@@ -2845,45 +2845,45 @@
         <v>57.5</v>
       </c>
       <c r="M19">
-        <v>7.449714499999999</v>
+        <v>8.0058834</v>
       </c>
       <c r="N19">
-        <v>50.0502855</v>
+        <v>49.4941166</v>
       </c>
       <c r="O19">
-        <v>13.2633256575</v>
+        <v>13.115940899</v>
       </c>
       <c r="P19">
-        <v>36.7869598425</v>
+        <v>36.378175701</v>
       </c>
       <c r="Q19">
-        <v>45.7869598425</v>
+        <v>45.378175701</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07205463605238707</v>
+        <v>0.0723010690478383</v>
       </c>
       <c r="T19">
-        <v>0.6063426340043202</v>
+        <v>0.6120339272018082</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.265</v>
       </c>
       <c r="W19">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.718416591669387</v>
+        <v>7.182218017314616</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06647076661922741</v>
+        <v>0.06635140031497354</v>
       </c>
       <c r="C20">
-        <v>608.915092239336</v>
+        <v>602.3854685951876</v>
       </c>
       <c r="D20">
-        <v>746.993092239336</v>
+        <v>748.6544685951876</v>
       </c>
       <c r="E20">
-        <v>-314.4619999999999</v>
+        <v>-306.271</v>
       </c>
       <c r="F20">
-        <v>147.438</v>
+        <v>155.629</v>
       </c>
       <c r="G20">
         <v>9.359999999999999</v>
@@ -2927,28 +2927,28 @@
         <v>57.5</v>
       </c>
       <c r="M20">
-        <v>8.0058834</v>
+        <v>8.450654699999999</v>
       </c>
       <c r="N20">
-        <v>49.4941166</v>
+        <v>49.0493453</v>
       </c>
       <c r="O20">
-        <v>13.115940899</v>
+        <v>12.9980765045</v>
       </c>
       <c r="P20">
-        <v>36.378175701</v>
+        <v>36.0512687955</v>
       </c>
       <c r="Q20">
-        <v>45.378175701</v>
+        <v>45.0512687955</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0723010690478383</v>
+        <v>0.07255358680860931</v>
       </c>
       <c r="T20">
-        <v>0.6120339272018082</v>
+        <v>0.6178657461572588</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.182218017314616</v>
+        <v>6.80420654271911</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06635140031497354</v>
+        <v>0.06623203401071968</v>
       </c>
       <c r="C21">
-        <v>602.3854685951876</v>
+        <v>595.8632515093188</v>
       </c>
       <c r="D21">
-        <v>748.6544685951876</v>
+        <v>750.3232515093189</v>
       </c>
       <c r="E21">
-        <v>-306.271</v>
+        <v>-298.0799999999999</v>
       </c>
       <c r="F21">
-        <v>155.629</v>
+        <v>163.82</v>
       </c>
       <c r="G21">
         <v>9.359999999999999</v>
@@ -3009,28 +3009,28 @@
         <v>57.5</v>
       </c>
       <c r="M21">
-        <v>8.450654699999999</v>
+        <v>8.895426</v>
       </c>
       <c r="N21">
-        <v>49.0493453</v>
+        <v>48.604574</v>
       </c>
       <c r="O21">
-        <v>12.9980765045</v>
+        <v>12.88021211</v>
       </c>
       <c r="P21">
-        <v>36.0512687955</v>
+        <v>35.72436189</v>
       </c>
       <c r="Q21">
-        <v>45.0512687955</v>
+        <v>44.72436189</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07255358680860931</v>
+        <v>0.07281241751339959</v>
       </c>
       <c r="T21">
-        <v>0.6178657461572588</v>
+        <v>0.6238433605865957</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.80420654271911</v>
+        <v>6.463996215583155</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06623203401071968</v>
+        <v>0.06611266770646582</v>
       </c>
       <c r="C22">
-        <v>595.8632515093188</v>
+        <v>589.3484906209865</v>
       </c>
       <c r="D22">
-        <v>750.3232515093189</v>
+        <v>751.9994906209864</v>
       </c>
       <c r="E22">
-        <v>-298.0799999999999</v>
+        <v>-289.8889999999999</v>
       </c>
       <c r="F22">
-        <v>163.82</v>
+        <v>172.011</v>
       </c>
       <c r="G22">
         <v>9.359999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>57.5</v>
       </c>
       <c r="M22">
-        <v>8.895426</v>
+        <v>9.3401973</v>
       </c>
       <c r="N22">
-        <v>48.604574</v>
+        <v>48.1598027</v>
       </c>
       <c r="O22">
-        <v>12.88021211</v>
+        <v>12.7623477155</v>
       </c>
       <c r="P22">
-        <v>35.72436189</v>
+        <v>35.3974549845</v>
       </c>
       <c r="Q22">
-        <v>44.72436189</v>
+        <v>44.3974549845</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07281241751339959</v>
+        <v>0.07307780089426053</v>
       </c>
       <c r="T22">
-        <v>0.6238433605865957</v>
+        <v>0.629972307026802</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.463996215583155</v>
+        <v>6.156186871983957</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06611266770646582</v>
+        <v>0.06615500140221195</v>
       </c>
       <c r="C23">
-        <v>589.3484906209865</v>
+        <v>580.5621498977547</v>
       </c>
       <c r="D23">
-        <v>751.9994906209864</v>
+        <v>751.4041498977547</v>
       </c>
       <c r="E23">
-        <v>-289.889</v>
+        <v>-281.698</v>
       </c>
       <c r="F23">
-        <v>172.011</v>
+        <v>180.202</v>
       </c>
       <c r="G23">
         <v>9.359999999999999</v>
@@ -3173,45 +3173,45 @@
         <v>57.5</v>
       </c>
       <c r="M23">
-        <v>9.340197299999998</v>
+        <v>9.965170599999999</v>
       </c>
       <c r="N23">
-        <v>48.1598027</v>
+        <v>47.5348294</v>
       </c>
       <c r="O23">
-        <v>12.7623477155</v>
+        <v>12.596729791</v>
       </c>
       <c r="P23">
-        <v>35.3974549845</v>
+        <v>34.938099609</v>
       </c>
       <c r="Q23">
-        <v>44.3974549845</v>
+        <v>43.938099609</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07307780089426053</v>
+        <v>0.07334998897719482</v>
       </c>
       <c r="T23">
-        <v>0.629972307026802</v>
+        <v>0.636258405939834</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.265</v>
       </c>
       <c r="W23">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.156186871983958</v>
+        <v>5.770096901301419</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06615500140221195</v>
+        <v>0.0660429850979581</v>
       </c>
       <c r="C24">
-        <v>580.5621498977547</v>
+        <v>573.9484974810806</v>
       </c>
       <c r="D24">
-        <v>751.4041498977547</v>
+        <v>752.9814974810806</v>
       </c>
       <c r="E24">
-        <v>-281.698</v>
+        <v>-273.5069999999999</v>
       </c>
       <c r="F24">
-        <v>180.202</v>
+        <v>188.393</v>
       </c>
       <c r="G24">
         <v>9.359999999999999</v>
@@ -3255,28 +3255,28 @@
         <v>57.5</v>
       </c>
       <c r="M24">
-        <v>9.965170599999999</v>
+        <v>10.4181329</v>
       </c>
       <c r="N24">
-        <v>47.5348294</v>
+        <v>47.0818671</v>
       </c>
       <c r="O24">
-        <v>12.596729791</v>
+        <v>12.4766947815</v>
       </c>
       <c r="P24">
-        <v>34.938099609</v>
+        <v>34.6051723185</v>
       </c>
       <c r="Q24">
-        <v>43.938099609</v>
+        <v>43.6051723185</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07334998897719482</v>
+        <v>0.07362924688046506</v>
       </c>
       <c r="T24">
-        <v>0.636258405939834</v>
+        <v>0.6427077801493083</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.770096901301419</v>
+        <v>5.519223122983965</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0660429850979581</v>
+        <v>0.06593096879370423</v>
       </c>
       <c r="C25">
-        <v>573.9484974810806</v>
+        <v>567.3414813313177</v>
       </c>
       <c r="D25">
-        <v>752.9814974810806</v>
+        <v>754.5654813313178</v>
       </c>
       <c r="E25">
-        <v>-273.5069999999999</v>
+        <v>-265.3159999999999</v>
       </c>
       <c r="F25">
-        <v>188.393</v>
+        <v>196.584</v>
       </c>
       <c r="G25">
         <v>9.359999999999999</v>
@@ -3337,28 +3337,28 @@
         <v>57.5</v>
       </c>
       <c r="M25">
-        <v>10.4181329</v>
+        <v>10.8710952</v>
       </c>
       <c r="N25">
-        <v>47.0818671</v>
+        <v>46.6289048</v>
       </c>
       <c r="O25">
-        <v>12.4766947815</v>
+        <v>12.356659772</v>
       </c>
       <c r="P25">
-        <v>34.6051723185</v>
+        <v>34.272245028</v>
       </c>
       <c r="Q25">
-        <v>43.6051723185</v>
+        <v>43.272245028</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07362924688046506</v>
+        <v>0.07391585367592662</v>
       </c>
       <c r="T25">
-        <v>0.6427077801493083</v>
+        <v>0.6493268747327163</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.519223122983965</v>
+        <v>5.289255492859634</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06593096879370423</v>
+        <v>0.06581895248945038</v>
       </c>
       <c r="C26">
-        <v>567.3414813313178</v>
+        <v>560.7411434172218</v>
       </c>
       <c r="D26">
-        <v>754.5654813313178</v>
+        <v>756.1561434172218</v>
       </c>
       <c r="E26">
-        <v>-265.3159999999999</v>
+        <v>-257.1249999999999</v>
       </c>
       <c r="F26">
-        <v>196.584</v>
+        <v>204.775</v>
       </c>
       <c r="G26">
         <v>9.359999999999999</v>
@@ -3419,28 +3419,28 @@
         <v>57.5</v>
       </c>
       <c r="M26">
-        <v>10.8710952</v>
+        <v>11.3240575</v>
       </c>
       <c r="N26">
-        <v>46.6289048</v>
+        <v>46.1759425</v>
       </c>
       <c r="O26">
-        <v>12.356659772</v>
+        <v>12.2366247625</v>
       </c>
       <c r="P26">
-        <v>34.272245028</v>
+        <v>33.93931773750001</v>
       </c>
       <c r="Q26">
-        <v>43.272245028</v>
+        <v>42.93931773750001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07391585367592662</v>
+        <v>0.07421010331926717</v>
       </c>
       <c r="T26">
-        <v>0.6493268747327163</v>
+        <v>0.6561224785050153</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.289255492859635</v>
+        <v>5.077685273145249</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06581895248945038</v>
+        <v>0.06570693618519652</v>
       </c>
       <c r="C27">
-        <v>560.7411434172218</v>
+        <v>554.1475260621854</v>
       </c>
       <c r="D27">
-        <v>756.1561434172218</v>
+        <v>757.7535260621854</v>
       </c>
       <c r="E27">
-        <v>-257.1249999999999</v>
+        <v>-248.9339999999999</v>
       </c>
       <c r="F27">
-        <v>204.775</v>
+        <v>212.966</v>
       </c>
       <c r="G27">
         <v>9.359999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>57.5</v>
       </c>
       <c r="M27">
-        <v>11.3240575</v>
+        <v>11.7770198</v>
       </c>
       <c r="N27">
-        <v>46.1759425</v>
+        <v>45.7229802</v>
       </c>
       <c r="O27">
-        <v>12.2366247625</v>
+        <v>12.116589753</v>
       </c>
       <c r="P27">
-        <v>33.93931773750001</v>
+        <v>33.606390447</v>
       </c>
       <c r="Q27">
-        <v>42.93931773750001</v>
+        <v>42.606390447</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07421010331926717</v>
+        <v>0.07451230565567096</v>
       </c>
       <c r="T27">
-        <v>0.6561224785050153</v>
+        <v>0.663101747244133</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.077685273145249</v>
+        <v>4.882389685716586</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06570693618519652</v>
+        <v>0.06559491988094265</v>
       </c>
       <c r="C28">
-        <v>554.1475260621854</v>
+        <v>547.5606719479915</v>
       </c>
       <c r="D28">
-        <v>757.7535260621854</v>
+        <v>759.3576719479915</v>
       </c>
       <c r="E28">
-        <v>-248.9339999999999</v>
+        <v>-240.7429999999999</v>
       </c>
       <c r="F28">
-        <v>212.966</v>
+        <v>221.157</v>
       </c>
       <c r="G28">
         <v>9.359999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>57.5</v>
       </c>
       <c r="M28">
-        <v>11.7770198</v>
+        <v>12.2299821</v>
       </c>
       <c r="N28">
-        <v>45.7229802</v>
+        <v>45.2700179</v>
       </c>
       <c r="O28">
-        <v>12.116589753</v>
+        <v>11.9965547435</v>
       </c>
       <c r="P28">
-        <v>33.606390447</v>
+        <v>33.2734631565</v>
       </c>
       <c r="Q28">
-        <v>42.606390447</v>
+        <v>42.2734631565</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07451230565567096</v>
+        <v>0.07482278750814061</v>
       </c>
       <c r="T28">
-        <v>0.663101747244133</v>
+        <v>0.6702722288254181</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.882389685716586</v>
+        <v>4.701560438097452</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06559491988094265</v>
+        <v>0.06548290357668879</v>
       </c>
       <c r="C29">
-        <v>547.5606719479915</v>
+        <v>540.980624118615</v>
       </c>
       <c r="D29">
-        <v>759.3576719479915</v>
+        <v>760.9686241186149</v>
       </c>
       <c r="E29">
-        <v>-240.7429999999999</v>
+        <v>-232.5519999999999</v>
       </c>
       <c r="F29">
-        <v>221.157</v>
+        <v>229.348</v>
       </c>
       <c r="G29">
         <v>9.359999999999999</v>
@@ -3665,28 +3665,28 @@
         <v>57.5</v>
       </c>
       <c r="M29">
-        <v>12.2299821</v>
+        <v>12.6829444</v>
       </c>
       <c r="N29">
-        <v>45.2700179</v>
+        <v>44.8170556</v>
       </c>
       <c r="O29">
-        <v>11.9965547435</v>
+        <v>11.876519734</v>
       </c>
       <c r="P29">
-        <v>33.2734631565</v>
+        <v>32.940535866</v>
       </c>
       <c r="Q29">
-        <v>42.2734631565</v>
+        <v>41.940535866</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07482278750814061</v>
+        <v>0.07514189385651221</v>
       </c>
       <c r="T29">
-        <v>0.6702722288254181</v>
+        <v>0.6776418904506282</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.701560438097452</v>
+        <v>4.533647565308257</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06548290357668879</v>
+        <v>0.06590376227243493</v>
       </c>
       <c r="C30">
-        <v>540.980624118615</v>
+        <v>526.7722057227883</v>
       </c>
       <c r="D30">
-        <v>760.9686241186149</v>
+        <v>754.9512057227882</v>
       </c>
       <c r="E30">
-        <v>-232.5519999999999</v>
+        <v>-224.3609999999999</v>
       </c>
       <c r="F30">
-        <v>229.348</v>
+        <v>237.539</v>
       </c>
       <c r="G30">
         <v>9.359999999999999</v>
@@ -3747,45 +3747,45 @@
         <v>57.5</v>
       </c>
       <c r="M30">
-        <v>12.6829444</v>
+        <v>13.7297542</v>
       </c>
       <c r="N30">
-        <v>44.8170556</v>
+        <v>43.7702458</v>
       </c>
       <c r="O30">
-        <v>11.876519734</v>
+        <v>11.599115137</v>
       </c>
       <c r="P30">
-        <v>32.940535866</v>
+        <v>32.171130663</v>
       </c>
       <c r="Q30">
-        <v>41.940535866</v>
+        <v>41.171130663</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07514189385651221</v>
+        <v>0.07546998911610553</v>
       </c>
       <c r="T30">
-        <v>0.6776418904506282</v>
+        <v>0.6852191481779566</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.265</v>
       </c>
       <c r="W30">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.533647565308257</v>
+        <v>4.187984661808439</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06590376227243493</v>
+        <v>0.06581012096818105</v>
       </c>
       <c r="C31">
-        <v>526.7722057227883</v>
+        <v>519.9118386904611</v>
       </c>
       <c r="D31">
-        <v>754.9512057227882</v>
+        <v>756.2818386904611</v>
       </c>
       <c r="E31">
-        <v>-224.361</v>
+        <v>-216.17</v>
       </c>
       <c r="F31">
-        <v>237.539</v>
+        <v>245.73</v>
       </c>
       <c r="G31">
         <v>9.359999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>57.5</v>
       </c>
       <c r="M31">
-        <v>13.7297542</v>
+        <v>14.203194</v>
       </c>
       <c r="N31">
-        <v>43.7702458</v>
+        <v>43.296806</v>
       </c>
       <c r="O31">
-        <v>11.599115137</v>
+        <v>11.47365359</v>
       </c>
       <c r="P31">
-        <v>32.171130663</v>
+        <v>31.82315241</v>
       </c>
       <c r="Q31">
-        <v>41.171130663</v>
+        <v>40.82315241000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07546998911610553</v>
+        <v>0.07580745852597294</v>
       </c>
       <c r="T31">
-        <v>0.6852191481779566</v>
+        <v>0.6930128989832087</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.187984661808439</v>
+        <v>4.048385173081492</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06581012096818105</v>
+        <v>0.06651395466392719</v>
       </c>
       <c r="C32">
-        <v>519.9118386904611</v>
+        <v>501.8328030771509</v>
       </c>
       <c r="D32">
-        <v>756.2818386904611</v>
+        <v>746.3938030771508</v>
       </c>
       <c r="E32">
-        <v>-216.17</v>
+        <v>-207.979</v>
       </c>
       <c r="F32">
-        <v>245.73</v>
+        <v>253.921</v>
       </c>
       <c r="G32">
         <v>9.359999999999999</v>
@@ -3911,45 +3911,45 @@
         <v>57.5</v>
       </c>
       <c r="M32">
-        <v>14.203194</v>
+        <v>15.5653573</v>
       </c>
       <c r="N32">
-        <v>43.296806</v>
+        <v>41.9346427</v>
       </c>
       <c r="O32">
-        <v>11.47365359</v>
+        <v>11.1126803155</v>
       </c>
       <c r="P32">
-        <v>31.82315241</v>
+        <v>30.8219623845</v>
       </c>
       <c r="Q32">
-        <v>40.82315241000001</v>
+        <v>39.8219623845</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07580745852597294</v>
+        <v>0.0761547096578655</v>
       </c>
       <c r="T32">
-        <v>0.6930128989832087</v>
+        <v>0.701032555608903</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.265</v>
       </c>
       <c r="W32">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.048385173081492</v>
+        <v>3.69410087361117</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06651395466392719</v>
+        <v>0.06644603835967333</v>
       </c>
       <c r="C33">
-        <v>501.8328030771509</v>
+        <v>494.5846618121528</v>
       </c>
       <c r="D33">
-        <v>746.3938030771508</v>
+        <v>747.3366618121528</v>
       </c>
       <c r="E33">
-        <v>-207.979</v>
+        <v>-199.788</v>
       </c>
       <c r="F33">
-        <v>253.921</v>
+        <v>262.112</v>
       </c>
       <c r="G33">
         <v>9.359999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>57.5</v>
       </c>
       <c r="M33">
-        <v>15.5653573</v>
+        <v>16.0674656</v>
       </c>
       <c r="N33">
-        <v>41.9346427</v>
+        <v>41.4325344</v>
       </c>
       <c r="O33">
-        <v>11.1126803155</v>
+        <v>10.979621616</v>
       </c>
       <c r="P33">
-        <v>30.8219623845</v>
+        <v>30.452912784</v>
       </c>
       <c r="Q33">
-        <v>39.8219623845</v>
+        <v>39.452912784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0761547096578655</v>
+        <v>0.07651217405834315</v>
       </c>
       <c r="T33">
-        <v>0.701032555608903</v>
+        <v>0.7092880844882943</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.69410087361117</v>
+        <v>3.578660221310821</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06644603835967333</v>
+        <v>0.06705726205541948</v>
       </c>
       <c r="C34">
-        <v>494.5846618121528</v>
+        <v>477.9930370097997</v>
       </c>
       <c r="D34">
-        <v>747.3366618121528</v>
+        <v>738.9360370097996</v>
       </c>
       <c r="E34">
-        <v>-199.788</v>
+        <v>-191.5969999999999</v>
       </c>
       <c r="F34">
-        <v>262.112</v>
+        <v>270.303</v>
       </c>
       <c r="G34">
         <v>9.359999999999999</v>
@@ -4075,45 +4075,45 @@
         <v>57.5</v>
       </c>
       <c r="M34">
-        <v>16.0674656</v>
+        <v>17.3264223</v>
       </c>
       <c r="N34">
-        <v>41.4325344</v>
+        <v>40.1735777</v>
       </c>
       <c r="O34">
-        <v>10.979621616</v>
+        <v>10.6459980905</v>
       </c>
       <c r="P34">
-        <v>30.452912784</v>
+        <v>29.52757960949999</v>
       </c>
       <c r="Q34">
-        <v>39.452912784</v>
+        <v>38.52757960949999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07651217405834315</v>
+        <v>0.07688030903793952</v>
       </c>
       <c r="T34">
-        <v>0.7092880844882943</v>
+        <v>0.7177900470655777</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.265</v>
       </c>
       <c r="W34">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.578660221310821</v>
+        <v>3.318630875111476</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06705726205541948</v>
+        <v>0.06700992575116561</v>
       </c>
       <c r="C35">
-        <v>477.9930370097997</v>
+        <v>470.4458719604751</v>
       </c>
       <c r="D35">
-        <v>738.9360370097996</v>
+        <v>739.5798719604751</v>
       </c>
       <c r="E35">
-        <v>-191.5969999999999</v>
+        <v>-183.4059999999999</v>
       </c>
       <c r="F35">
-        <v>270.303</v>
+        <v>278.494</v>
       </c>
       <c r="G35">
         <v>9.359999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>57.5</v>
       </c>
       <c r="M35">
-        <v>17.3264223</v>
+        <v>17.8514654</v>
       </c>
       <c r="N35">
-        <v>40.1735777</v>
+        <v>39.6485346</v>
       </c>
       <c r="O35">
-        <v>10.6459980905</v>
+        <v>10.506861669</v>
       </c>
       <c r="P35">
-        <v>29.52757960949999</v>
+        <v>29.141672931</v>
       </c>
       <c r="Q35">
-        <v>38.52757960949999</v>
+        <v>38.141672931</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07688030903793952</v>
+        <v>0.07725959962297821</v>
       </c>
       <c r="T35">
-        <v>0.7177900470655777</v>
+        <v>0.7265496448724758</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.318630875111476</v>
+        <v>3.221024084667022</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06700992575116561</v>
+        <v>0.06696258944691175</v>
       </c>
       <c r="C36">
-        <v>470.4458719604751</v>
+        <v>462.8998298363082</v>
       </c>
       <c r="D36">
-        <v>739.5798719604751</v>
+        <v>740.2248298363082</v>
       </c>
       <c r="E36">
-        <v>-183.4059999999999</v>
+        <v>-175.2149999999999</v>
       </c>
       <c r="F36">
-        <v>278.494</v>
+        <v>286.685</v>
       </c>
       <c r="G36">
         <v>9.359999999999999</v>
@@ -4239,28 +4239,28 @@
         <v>57.5</v>
       </c>
       <c r="M36">
-        <v>17.8514654</v>
+        <v>18.3765085</v>
       </c>
       <c r="N36">
-        <v>39.6485346</v>
+        <v>39.1234915</v>
       </c>
       <c r="O36">
-        <v>10.506861669</v>
+        <v>10.3677252475</v>
       </c>
       <c r="P36">
-        <v>29.141672931</v>
+        <v>28.7557662525</v>
       </c>
       <c r="Q36">
-        <v>38.141672931</v>
+        <v>37.7557662525</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07725959962297821</v>
+        <v>0.07765056068755655</v>
       </c>
       <c r="T36">
-        <v>0.7265496448724758</v>
+        <v>0.7355787687657399</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.221024084667022</v>
+        <v>3.128994825105107</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06696258944691175</v>
+        <v>0.06691525314265789</v>
       </c>
       <c r="C37">
-        <v>462.8998298363082</v>
+        <v>455.3549135776368</v>
       </c>
       <c r="D37">
-        <v>740.2248298363082</v>
+        <v>740.8709135776368</v>
       </c>
       <c r="E37">
-        <v>-175.2149999999999</v>
+        <v>-167.0239999999999</v>
       </c>
       <c r="F37">
-        <v>286.685</v>
+        <v>294.876</v>
       </c>
       <c r="G37">
         <v>9.359999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>57.5</v>
       </c>
       <c r="M37">
-        <v>18.3765085</v>
+        <v>18.9015516</v>
       </c>
       <c r="N37">
-        <v>39.1234915</v>
+        <v>38.5984484</v>
       </c>
       <c r="O37">
-        <v>10.3677252475</v>
+        <v>10.228588826</v>
       </c>
       <c r="P37">
-        <v>28.7557662525</v>
+        <v>28.369859574</v>
       </c>
       <c r="Q37">
-        <v>37.7557662525</v>
+        <v>37.369859574</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07765056068755655</v>
+        <v>0.07805373928540296</v>
       </c>
       <c r="T37">
-        <v>0.7355787687657399</v>
+        <v>0.7448900527806687</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.128994825105107</v>
+        <v>3.04207830218552</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06691525314265789</v>
+        <v>0.06898912683840402</v>
       </c>
       <c r="C38">
-        <v>455.3549135776368</v>
+        <v>419.8767696035091</v>
       </c>
       <c r="D38">
-        <v>740.8709135776368</v>
+        <v>713.583769603509</v>
       </c>
       <c r="E38">
-        <v>-167.0239999999999</v>
+        <v>-158.833</v>
       </c>
       <c r="F38">
-        <v>294.876</v>
+        <v>303.067</v>
       </c>
       <c r="G38">
         <v>9.359999999999999</v>
@@ -4403,45 +4403,45 @@
         <v>57.5</v>
       </c>
       <c r="M38">
-        <v>18.9015516</v>
+        <v>21.7905173</v>
       </c>
       <c r="N38">
-        <v>38.5984484</v>
+        <v>35.7094827</v>
       </c>
       <c r="O38">
-        <v>10.228588826</v>
+        <v>9.4630129155</v>
       </c>
       <c r="P38">
-        <v>28.369859574</v>
+        <v>26.2464697845</v>
       </c>
       <c r="Q38">
-        <v>37.369859574</v>
+        <v>35.2464697845</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07805373928540296</v>
+        <v>0.07846971720381592</v>
       </c>
       <c r="T38">
-        <v>0.7448900527806687</v>
+        <v>0.7544969331135315</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.265</v>
       </c>
       <c r="W38">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.04207830218552</v>
+        <v>2.638762504275197</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06898912683840402</v>
+        <v>0.06899912053415017</v>
       </c>
       <c r="C39">
-        <v>419.8767696035091</v>
+        <v>411.5591423323918</v>
       </c>
       <c r="D39">
-        <v>713.583769603509</v>
+        <v>713.4571423323918</v>
       </c>
       <c r="E39">
-        <v>-158.833</v>
+        <v>-150.6419999999999</v>
       </c>
       <c r="F39">
-        <v>303.067</v>
+        <v>311.258</v>
       </c>
       <c r="G39">
         <v>9.359999999999999</v>
@@ -4485,28 +4485,28 @@
         <v>57.5</v>
       </c>
       <c r="M39">
-        <v>21.7905173</v>
+        <v>22.3794502</v>
       </c>
       <c r="N39">
-        <v>35.7094827</v>
+        <v>35.1205498</v>
       </c>
       <c r="O39">
-        <v>9.4630129155</v>
+        <v>9.306945697</v>
       </c>
       <c r="P39">
-        <v>26.2464697845</v>
+        <v>25.813604103</v>
       </c>
       <c r="Q39">
-        <v>35.2464697845</v>
+        <v>34.813604103</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07846971720381592</v>
+        <v>0.07889911376475833</v>
       </c>
       <c r="T39">
-        <v>0.7544969331135315</v>
+        <v>0.7644137128119706</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.638762504275197</v>
+        <v>2.569321385741639</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06899912053415017</v>
+        <v>0.06900911422989631</v>
       </c>
       <c r="C40">
-        <v>411.5591423323918</v>
+        <v>403.2415599939696</v>
       </c>
       <c r="D40">
-        <v>713.4571423323918</v>
+        <v>713.3305599939696</v>
       </c>
       <c r="E40">
-        <v>-150.6419999999999</v>
+        <v>-142.451</v>
       </c>
       <c r="F40">
-        <v>311.258</v>
+        <v>319.449</v>
       </c>
       <c r="G40">
         <v>9.359999999999999</v>
@@ -4567,28 +4567,28 @@
         <v>57.5</v>
       </c>
       <c r="M40">
-        <v>22.3794502</v>
+        <v>22.9683831</v>
       </c>
       <c r="N40">
-        <v>35.1205498</v>
+        <v>34.5316169</v>
       </c>
       <c r="O40">
-        <v>9.306945697</v>
+        <v>9.150878478500001</v>
       </c>
       <c r="P40">
-        <v>25.813604103</v>
+        <v>25.3807384215</v>
       </c>
       <c r="Q40">
-        <v>34.813604103</v>
+        <v>34.3807384215</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07889911376475833</v>
+        <v>0.07934258890146935</v>
       </c>
       <c r="T40">
-        <v>0.7644137128119706</v>
+        <v>0.7746556328283913</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.569321385741639</v>
+        <v>2.503441350209803</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06900911422989631</v>
+        <v>0.07016570792564245</v>
       </c>
       <c r="C41">
-        <v>403.2415599939696</v>
+        <v>380.6981924320135</v>
       </c>
       <c r="D41">
-        <v>713.3305599939696</v>
+        <v>698.9781924320134</v>
       </c>
       <c r="E41">
-        <v>-142.451</v>
+        <v>-134.2599999999999</v>
       </c>
       <c r="F41">
-        <v>319.449</v>
+        <v>327.64</v>
       </c>
       <c r="G41">
         <v>9.359999999999999</v>
@@ -4649,45 +4649,45 @@
         <v>57.5</v>
       </c>
       <c r="M41">
-        <v>22.9683831</v>
+        <v>24.835112</v>
       </c>
       <c r="N41">
-        <v>34.5316169</v>
+        <v>32.664888</v>
       </c>
       <c r="O41">
-        <v>9.150878478500001</v>
+        <v>8.65619532</v>
       </c>
       <c r="P41">
-        <v>25.3807384215</v>
+        <v>24.00869268</v>
       </c>
       <c r="Q41">
-        <v>34.3807384215</v>
+        <v>33.00869268</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07934258890146935</v>
+        <v>0.07980084654273741</v>
       </c>
       <c r="T41">
-        <v>0.7746556328283913</v>
+        <v>0.7852389501786928</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.265</v>
       </c>
       <c r="W41">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.503441350209803</v>
+        <v>2.315270412309797</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07016570792564245</v>
+        <v>0.07020436662138858</v>
       </c>
       <c r="C42">
-        <v>380.6981924320135</v>
+        <v>372.0374381453544</v>
       </c>
       <c r="D42">
-        <v>698.9781924320134</v>
+        <v>698.5084381453544</v>
       </c>
       <c r="E42">
-        <v>-134.2599999999999</v>
+        <v>-126.069</v>
       </c>
       <c r="F42">
-        <v>327.64</v>
+        <v>335.831</v>
       </c>
       <c r="G42">
         <v>9.359999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>57.5</v>
       </c>
       <c r="M42">
-        <v>24.835112</v>
+        <v>25.4559898</v>
       </c>
       <c r="N42">
-        <v>32.664888</v>
+        <v>32.0440102</v>
       </c>
       <c r="O42">
-        <v>8.65619532</v>
+        <v>8.491662703000001</v>
       </c>
       <c r="P42">
-        <v>24.00869268</v>
+        <v>23.552347497</v>
       </c>
       <c r="Q42">
-        <v>33.00869268</v>
+        <v>32.552347497</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07980084654273741</v>
+        <v>0.08027463834133658</v>
       </c>
       <c r="T42">
-        <v>0.7852389501786928</v>
+        <v>0.7961810240493434</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.315270412309797</v>
+        <v>2.258800402253461</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07020436662138858</v>
+        <v>0.07024302531713472</v>
       </c>
       <c r="C43">
-        <v>372.0374381453544</v>
+        <v>363.3773148394307</v>
       </c>
       <c r="D43">
-        <v>698.5084381453544</v>
+        <v>698.0393148394306</v>
       </c>
       <c r="E43">
-        <v>-126.069</v>
+        <v>-117.8779999999999</v>
       </c>
       <c r="F43">
-        <v>335.831</v>
+        <v>344.022</v>
       </c>
       <c r="G43">
         <v>9.359999999999999</v>
@@ -4813,28 +4813,28 @@
         <v>57.5</v>
       </c>
       <c r="M43">
-        <v>25.4559898</v>
+        <v>26.0768676</v>
       </c>
       <c r="N43">
-        <v>32.0440102</v>
+        <v>31.4231324</v>
       </c>
       <c r="O43">
-        <v>8.491662703000001</v>
+        <v>8.327130086</v>
       </c>
       <c r="P43">
-        <v>23.552347497</v>
+        <v>23.096002314</v>
       </c>
       <c r="Q43">
-        <v>32.552347497</v>
+        <v>32.096002314</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08027463834133658</v>
+        <v>0.0807647677881633</v>
       </c>
       <c r="T43">
-        <v>0.7961810240493434</v>
+        <v>0.8075004108120856</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.258800402253461</v>
+        <v>2.205019440295045</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07024302531713472</v>
+        <v>0.07028168401288086</v>
       </c>
       <c r="C44">
-        <v>363.3773148394307</v>
+        <v>354.7178212437816</v>
       </c>
       <c r="D44">
-        <v>698.0393148394306</v>
+        <v>697.5708212437816</v>
       </c>
       <c r="E44">
-        <v>-117.878</v>
+        <v>-109.687</v>
       </c>
       <c r="F44">
-        <v>344.0219999999999</v>
+        <v>352.213</v>
       </c>
       <c r="G44">
         <v>9.359999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>57.5</v>
       </c>
       <c r="M44">
-        <v>26.0768676</v>
+        <v>26.6977454</v>
       </c>
       <c r="N44">
-        <v>31.4231324</v>
+        <v>30.8022546</v>
       </c>
       <c r="O44">
-        <v>8.327130086000002</v>
+        <v>8.162597469000001</v>
       </c>
       <c r="P44">
-        <v>23.096002314</v>
+        <v>22.639657131</v>
       </c>
       <c r="Q44">
-        <v>32.096002314</v>
+        <v>31.639657131</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0807647677881633</v>
+        <v>0.0812720947594401</v>
       </c>
       <c r="T44">
-        <v>0.8075004108120856</v>
+        <v>0.8192169690401869</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.205019440295046</v>
+        <v>2.153739918427719</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07028168401288086</v>
+        <v>0.070320342708627</v>
       </c>
       <c r="C45">
-        <v>354.7178212437816</v>
+        <v>346.0589560913555</v>
       </c>
       <c r="D45">
-        <v>697.5708212437816</v>
+        <v>697.1029560913554</v>
       </c>
       <c r="E45">
-        <v>-109.687</v>
+        <v>-101.496</v>
       </c>
       <c r="F45">
-        <v>352.213</v>
+        <v>360.4039999999999</v>
       </c>
       <c r="G45">
         <v>9.359999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>57.5</v>
       </c>
       <c r="M45">
-        <v>26.6977454</v>
+        <v>27.3186232</v>
       </c>
       <c r="N45">
-        <v>30.8022546</v>
+        <v>30.1813768</v>
       </c>
       <c r="O45">
-        <v>8.162597469000001</v>
+        <v>7.998064852000001</v>
       </c>
       <c r="P45">
-        <v>22.639657131</v>
+        <v>22.183311948</v>
       </c>
       <c r="Q45">
-        <v>31.639657131</v>
+        <v>31.183311948</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0812720947594401</v>
+        <v>0.08179754055111964</v>
       </c>
       <c r="T45">
-        <v>0.8192169690401869</v>
+        <v>0.8313519757764349</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.153739918427719</v>
+        <v>2.104791283917998</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.070320342708627</v>
+        <v>0.07035900140437314</v>
       </c>
       <c r="C46">
-        <v>346.0589560913555</v>
+        <v>337.4007181184972</v>
       </c>
       <c r="D46">
-        <v>697.1029560913554</v>
+        <v>696.6357181184972</v>
       </c>
       <c r="E46">
-        <v>-101.496</v>
+        <v>-93.30499999999995</v>
       </c>
       <c r="F46">
-        <v>360.4039999999999</v>
+        <v>368.595</v>
       </c>
       <c r="G46">
         <v>9.359999999999999</v>
@@ -5059,28 +5059,28 @@
         <v>57.5</v>
       </c>
       <c r="M46">
-        <v>27.3186232</v>
+        <v>27.939501</v>
       </c>
       <c r="N46">
-        <v>30.1813768</v>
+        <v>29.560499</v>
       </c>
       <c r="O46">
-        <v>7.998064852000001</v>
+        <v>7.833532235000001</v>
       </c>
       <c r="P46">
-        <v>22.183311948</v>
+        <v>21.726966765</v>
       </c>
       <c r="Q46">
-        <v>31.183311948</v>
+        <v>30.726966765</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08179754055111964</v>
+        <v>0.0823420934624966</v>
       </c>
       <c r="T46">
-        <v>0.8313519757764349</v>
+        <v>0.8439282554849099</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.104791283917998</v>
+        <v>2.058018144275375</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07035900140437314</v>
+        <v>0.07039766010011927</v>
       </c>
       <c r="C47">
-        <v>337.4007181184972</v>
+        <v>328.7431060649375</v>
       </c>
       <c r="D47">
-        <v>696.6357181184972</v>
+        <v>696.1691060649375</v>
       </c>
       <c r="E47">
-        <v>-93.30499999999995</v>
+        <v>-85.11399999999992</v>
       </c>
       <c r="F47">
-        <v>368.595</v>
+        <v>376.786</v>
       </c>
       <c r="G47">
         <v>9.359999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>57.5</v>
       </c>
       <c r="M47">
-        <v>27.939501</v>
+        <v>28.5603788</v>
       </c>
       <c r="N47">
-        <v>29.560499</v>
+        <v>28.9396212</v>
       </c>
       <c r="O47">
-        <v>7.833532235000001</v>
+        <v>7.668999618</v>
       </c>
       <c r="P47">
-        <v>21.726966765</v>
+        <v>21.270621582</v>
       </c>
       <c r="Q47">
-        <v>30.726966765</v>
+        <v>30.270621582</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0823420934624966</v>
+        <v>0.08290681500022087</v>
       </c>
       <c r="T47">
-        <v>0.8439282554849099</v>
+        <v>0.856970323330736</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.058018144275375</v>
+        <v>2.013278619399824</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07039766010011927</v>
+        <v>0.07534170879586541</v>
       </c>
       <c r="C48">
-        <v>328.7431060649375</v>
+        <v>265.6225536481633</v>
       </c>
       <c r="D48">
-        <v>696.1691060649375</v>
+        <v>641.2395536481632</v>
       </c>
       <c r="E48">
-        <v>-85.11399999999992</v>
+        <v>-76.92299999999994</v>
       </c>
       <c r="F48">
-        <v>376.786</v>
+        <v>384.977</v>
       </c>
       <c r="G48">
         <v>9.359999999999999</v>
@@ -5223,45 +5223,45 @@
         <v>57.5</v>
       </c>
       <c r="M48">
-        <v>28.5603788</v>
+        <v>34.64793</v>
       </c>
       <c r="N48">
-        <v>28.9396212</v>
+        <v>22.85207</v>
       </c>
       <c r="O48">
-        <v>7.668999618</v>
+        <v>6.055798550000001</v>
       </c>
       <c r="P48">
-        <v>21.270621582</v>
+        <v>16.79627145</v>
       </c>
       <c r="Q48">
-        <v>30.270621582</v>
+        <v>25.79627145</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08290681500022087</v>
+        <v>0.08349284678465171</v>
       </c>
       <c r="T48">
-        <v>0.856970323330736</v>
+        <v>0.8705045446801781</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.265</v>
       </c>
       <c r="W48">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.013278619399824</v>
+        <v>1.65955080144759</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07534170879586541</v>
+        <v>0.07548473749161155</v>
       </c>
       <c r="C49">
-        <v>265.6225536481633</v>
+        <v>255.9711871539602</v>
       </c>
       <c r="D49">
-        <v>641.2395536481632</v>
+        <v>639.7791871539602</v>
       </c>
       <c r="E49">
-        <v>-76.92299999999994</v>
+        <v>-68.73199999999991</v>
       </c>
       <c r="F49">
-        <v>384.977</v>
+        <v>393.168</v>
       </c>
       <c r="G49">
         <v>9.359999999999999</v>
@@ -5305,28 +5305,28 @@
         <v>57.5</v>
       </c>
       <c r="M49">
-        <v>34.64793</v>
+        <v>35.38512</v>
       </c>
       <c r="N49">
-        <v>22.85207</v>
+        <v>22.11488</v>
       </c>
       <c r="O49">
-        <v>6.055798550000001</v>
+        <v>5.8604432</v>
       </c>
       <c r="P49">
-        <v>16.79627145</v>
+        <v>16.2544368</v>
       </c>
       <c r="Q49">
-        <v>25.79627145</v>
+        <v>25.2544368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08349284678465171</v>
+        <v>0.08410141825309914</v>
       </c>
       <c r="T49">
-        <v>0.8705045446801781</v>
+        <v>0.8845593130045988</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.65955080144759</v>
+        <v>1.624976826417432</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07548473749161155</v>
+        <v>0.07562776618735768</v>
       </c>
       <c r="C50">
-        <v>255.9711871539602</v>
+        <v>246.3264572571196</v>
       </c>
       <c r="D50">
-        <v>639.7791871539602</v>
+        <v>638.3254572571195</v>
       </c>
       <c r="E50">
-        <v>-68.73199999999997</v>
+        <v>-60.541</v>
       </c>
       <c r="F50">
-        <v>393.1679999999999</v>
+        <v>401.3589999999999</v>
       </c>
       <c r="G50">
         <v>9.359999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>57.5</v>
       </c>
       <c r="M50">
-        <v>35.38511999999999</v>
+        <v>36.12230999999999</v>
       </c>
       <c r="N50">
-        <v>22.11488000000001</v>
+        <v>21.37769000000001</v>
       </c>
       <c r="O50">
-        <v>5.860443200000002</v>
+        <v>5.665087850000003</v>
       </c>
       <c r="P50">
-        <v>16.2544368</v>
+        <v>15.71260215000001</v>
       </c>
       <c r="Q50">
-        <v>25.2544368</v>
+        <v>24.71260215000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08410141825309914</v>
+        <v>0.08473385526932879</v>
       </c>
       <c r="T50">
-        <v>0.8845593130045988</v>
+        <v>0.8991652487142907</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.624976826417432</v>
+        <v>1.591814034041566</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07562776618735768</v>
+        <v>0.07577079488310381</v>
       </c>
       <c r="C51">
-        <v>246.3264572571196</v>
+        <v>236.6883188204388</v>
       </c>
       <c r="D51">
-        <v>638.3254572571195</v>
+        <v>636.8783188204387</v>
       </c>
       <c r="E51">
-        <v>-60.541</v>
+        <v>-52.34999999999997</v>
       </c>
       <c r="F51">
-        <v>401.3589999999999</v>
+        <v>409.55</v>
       </c>
       <c r="G51">
         <v>9.359999999999999</v>
@@ -5469,28 +5469,28 @@
         <v>57.5</v>
       </c>
       <c r="M51">
-        <v>36.12230999999999</v>
+        <v>36.8595</v>
       </c>
       <c r="N51">
-        <v>21.37769000000001</v>
+        <v>20.6405</v>
       </c>
       <c r="O51">
-        <v>5.665087850000003</v>
+        <v>5.469732500000001</v>
       </c>
       <c r="P51">
-        <v>15.71260215000001</v>
+        <v>15.1707675</v>
       </c>
       <c r="Q51">
-        <v>24.71260215000001</v>
+        <v>24.1707675</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08473385526932879</v>
+        <v>0.08539158976620764</v>
       </c>
       <c r="T51">
-        <v>0.8991652487142907</v>
+        <v>0.9143554218523704</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.591814034041566</v>
+        <v>1.559977753360735</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07577079488310381</v>
+        <v>0.07591382357884996</v>
       </c>
       <c r="C52">
-        <v>236.6883188204388</v>
+        <v>227.0567271151091</v>
       </c>
       <c r="D52">
-        <v>636.8783188204387</v>
+        <v>635.4377271151091</v>
       </c>
       <c r="E52">
-        <v>-52.34999999999997</v>
+        <v>-44.15899999999993</v>
       </c>
       <c r="F52">
-        <v>409.55</v>
+        <v>417.741</v>
       </c>
       <c r="G52">
         <v>9.359999999999999</v>
@@ -5551,28 +5551,28 @@
         <v>57.5</v>
       </c>
       <c r="M52">
-        <v>36.8595</v>
+        <v>37.59669</v>
       </c>
       <c r="N52">
-        <v>20.6405</v>
+        <v>19.90331</v>
       </c>
       <c r="O52">
-        <v>5.469732500000001</v>
+        <v>5.274377150000001</v>
       </c>
       <c r="P52">
-        <v>15.1707675</v>
+        <v>14.62893285</v>
       </c>
       <c r="Q52">
-        <v>24.1707675</v>
+        <v>23.62893285000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08539158976620764</v>
+        <v>0.08607617056908157</v>
       </c>
       <c r="T52">
-        <v>0.9143554218523704</v>
+        <v>0.9301656020573107</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.559977753360735</v>
+        <v>1.52938995427523</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07591382357884996</v>
+        <v>0.09964491896948174</v>
       </c>
       <c r="C53">
-        <v>227.0567271151091</v>
+        <v>45.46357946267176</v>
       </c>
       <c r="D53">
-        <v>635.4377271151091</v>
+        <v>462.0355794626717</v>
       </c>
       <c r="E53">
-        <v>-44.15899999999993</v>
+        <v>-35.96799999999996</v>
       </c>
       <c r="F53">
-        <v>417.741</v>
+        <v>425.932</v>
       </c>
       <c r="G53">
         <v>9.359999999999999</v>
@@ -5633,45 +5633,45 @@
         <v>57.5</v>
       </c>
       <c r="M53">
-        <v>37.59669</v>
+        <v>62.5268176</v>
       </c>
       <c r="N53">
-        <v>19.90331</v>
+        <v>-5.026817600000001</v>
       </c>
       <c r="O53">
-        <v>5.274377150000001</v>
+        <v>-1.332106664</v>
       </c>
       <c r="P53">
-        <v>14.62893285</v>
+        <v>-3.694710936000001</v>
       </c>
       <c r="Q53">
-        <v>23.62893285000001</v>
+        <v>5.305289063999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08607617056908157</v>
+        <v>0.08731594516314273</v>
       </c>
       <c r="T53">
-        <v>0.9301656020573107</v>
+        <v>0.9587978097723494</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.265</v>
+        <v>0.243695434772935</v>
       </c>
       <c r="W53">
-        <v>0.06615</v>
+        <v>0.1110255101753332</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.52938995427523</v>
+        <v>0.9196054142374903</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09964491896948174</v>
+        <v>0.1006549189694818</v>
       </c>
       <c r="C54">
-        <v>45.46357946267176</v>
+        <v>31.96806526059976</v>
       </c>
       <c r="D54">
-        <v>462.0355794626717</v>
+        <v>456.7310652605997</v>
       </c>
       <c r="E54">
-        <v>-35.96799999999996</v>
+        <v>-27.77699999999993</v>
       </c>
       <c r="F54">
-        <v>425.932</v>
+        <v>434.123</v>
       </c>
       <c r="G54">
         <v>9.359999999999999</v>
@@ -5715,37 +5715,37 @@
         <v>57.5</v>
       </c>
       <c r="M54">
-        <v>62.5268176</v>
+        <v>63.7292564</v>
       </c>
       <c r="N54">
-        <v>-5.026817600000001</v>
+        <v>-6.229256400000004</v>
       </c>
       <c r="O54">
-        <v>-1.332106664</v>
+        <v>-1.650752946000001</v>
       </c>
       <c r="P54">
-        <v>-3.694710936000001</v>
+        <v>-4.578503454000003</v>
       </c>
       <c r="Q54">
-        <v>5.305289063999999</v>
+        <v>4.421496545999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08731594516314273</v>
+        <v>0.08819926314533727</v>
       </c>
       <c r="T54">
-        <v>0.9587978097723494</v>
+        <v>0.9791977631717611</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.243695434772935</v>
+        <v>0.2390974077017475</v>
       </c>
       <c r="W54">
-        <v>0.1110255101753332</v>
+        <v>0.1117005005493835</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9196054142374903</v>
+        <v>0.9022543686858395</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1006549189694818</v>
+        <v>0.1016649189694818</v>
       </c>
       <c r="C55">
-        <v>31.96806526059976</v>
+        <v>18.59296816504798</v>
       </c>
       <c r="D55">
-        <v>456.7310652605997</v>
+        <v>451.5469681650479</v>
       </c>
       <c r="E55">
-        <v>-27.77699999999993</v>
+        <v>-19.58599999999996</v>
       </c>
       <c r="F55">
-        <v>434.123</v>
+        <v>442.314</v>
       </c>
       <c r="G55">
         <v>9.359999999999999</v>
@@ -5797,37 +5797,37 @@
         <v>57.5</v>
       </c>
       <c r="M55">
-        <v>63.7292564</v>
+        <v>64.93169520000001</v>
       </c>
       <c r="N55">
-        <v>-6.229256400000004</v>
+        <v>-7.431695200000007</v>
       </c>
       <c r="O55">
-        <v>-1.650752946000001</v>
+        <v>-1.969399228000002</v>
       </c>
       <c r="P55">
-        <v>-4.578503454000003</v>
+        <v>-5.462295972000005</v>
       </c>
       <c r="Q55">
-        <v>4.421496545999997</v>
+        <v>3.537704027999995</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08819926314533727</v>
+        <v>0.08912098625719242</v>
       </c>
       <c r="T55">
-        <v>0.9791977631717611</v>
+        <v>1.000484671066799</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2390974077017475</v>
+        <v>0.2346696779294929</v>
       </c>
       <c r="W55">
-        <v>0.1117005005493835</v>
+        <v>0.1123504912799504</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9022543686858395</v>
+        <v>0.8855459544509166</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1016649189694818</v>
+        <v>0.1026749189694817</v>
       </c>
       <c r="C56">
-        <v>18.59296816504798</v>
+        <v>5.334233834290501</v>
       </c>
       <c r="D56">
-        <v>451.5469681650479</v>
+        <v>446.4792338342905</v>
       </c>
       <c r="E56">
-        <v>-19.58599999999996</v>
+        <v>-11.39499999999992</v>
       </c>
       <c r="F56">
-        <v>442.314</v>
+        <v>450.505</v>
       </c>
       <c r="G56">
         <v>9.359999999999999</v>
@@ -5879,37 +5879,37 @@
         <v>57.5</v>
       </c>
       <c r="M56">
-        <v>64.93169520000001</v>
+        <v>66.134134</v>
       </c>
       <c r="N56">
-        <v>-7.431695200000007</v>
+        <v>-8.634134000000003</v>
       </c>
       <c r="O56">
-        <v>-1.969399228000002</v>
+        <v>-2.288045510000001</v>
       </c>
       <c r="P56">
-        <v>-5.462295972000005</v>
+        <v>-6.346088490000002</v>
       </c>
       <c r="Q56">
-        <v>3.537704027999995</v>
+        <v>2.653911509999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08912098625719242</v>
+        <v>0.09008367484068558</v>
       </c>
       <c r="T56">
-        <v>1.000484671066799</v>
+        <v>1.022717663757173</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2346696779294929</v>
+        <v>0.230402956512593</v>
       </c>
       <c r="W56">
-        <v>0.1123504912799504</v>
+        <v>0.1129768459839514</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8855459544509166</v>
+        <v>0.8694451189154453</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1026749189694817</v>
+        <v>0.1036849189694818</v>
       </c>
       <c r="C57">
-        <v>5.334233834290501</v>
+        <v>-7.812012085091794</v>
       </c>
       <c r="D57">
-        <v>446.4792338342905</v>
+        <v>441.5239879149082</v>
       </c>
       <c r="E57">
-        <v>-11.39499999999992</v>
+        <v>-3.203999999999951</v>
       </c>
       <c r="F57">
-        <v>450.505</v>
+        <v>458.696</v>
       </c>
       <c r="G57">
         <v>9.359999999999999</v>
@@ -5961,37 +5961,37 @@
         <v>57.5</v>
       </c>
       <c r="M57">
-        <v>66.134134</v>
+        <v>67.3365728</v>
       </c>
       <c r="N57">
-        <v>-8.634134000000003</v>
+        <v>-9.836572799999999</v>
       </c>
       <c r="O57">
-        <v>-2.288045510000001</v>
+        <v>-2.606691792</v>
       </c>
       <c r="P57">
-        <v>-6.346088490000002</v>
+        <v>-7.229881008</v>
       </c>
       <c r="Q57">
-        <v>2.653911509999998</v>
+        <v>1.770118992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09008367484068558</v>
+        <v>0.09109012199615571</v>
       </c>
       <c r="T57">
-        <v>1.022717663757173</v>
+        <v>1.045961247024381</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.230402956512593</v>
+        <v>0.2262886180034396</v>
       </c>
       <c r="W57">
-        <v>0.1129768459839514</v>
+        <v>0.1135808308770951</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8694451189154453</v>
+        <v>0.8539193132205267</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1036849189694818</v>
+        <v>0.1046949189694818</v>
       </c>
       <c r="C58">
-        <v>-7.812012085091794</v>
+        <v>-20.84947383657038</v>
       </c>
       <c r="D58">
-        <v>441.5239879149082</v>
+        <v>436.6775261634296</v>
       </c>
       <c r="E58">
-        <v>-3.203999999999951</v>
+        <v>4.98700000000008</v>
       </c>
       <c r="F58">
-        <v>458.696</v>
+        <v>466.887</v>
       </c>
       <c r="G58">
         <v>9.359999999999999</v>
@@ -6043,37 +6043,37 @@
         <v>57.5</v>
       </c>
       <c r="M58">
-        <v>67.3365728</v>
+        <v>68.53901160000001</v>
       </c>
       <c r="N58">
-        <v>-9.836572799999999</v>
+        <v>-11.03901160000001</v>
       </c>
       <c r="O58">
-        <v>-2.606691792</v>
+        <v>-2.925338074000003</v>
       </c>
       <c r="P58">
-        <v>-7.229881008</v>
+        <v>-8.113673526000007</v>
       </c>
       <c r="Q58">
-        <v>1.770118992</v>
+        <v>0.8863264739999934</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09109012199615571</v>
+        <v>0.09214338064722911</v>
       </c>
       <c r="T58">
-        <v>1.045961247024381</v>
+        <v>1.070285927187739</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2262886180034396</v>
+        <v>0.2223186422489933</v>
       </c>
       <c r="W58">
-        <v>0.1135808308770951</v>
+        <v>0.1141636233178478</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8539193132205267</v>
+        <v>0.8389382726377104</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1046949189694818</v>
+        <v>0.1057049189694818</v>
       </c>
       <c r="C59">
-        <v>-20.84947383657038</v>
+        <v>-33.78169478850174</v>
       </c>
       <c r="D59">
-        <v>436.6775261634296</v>
+        <v>431.9363052114983</v>
       </c>
       <c r="E59">
-        <v>4.98700000000008</v>
+        <v>13.17800000000011</v>
       </c>
       <c r="F59">
-        <v>466.887</v>
+        <v>475.078</v>
       </c>
       <c r="G59">
         <v>9.359999999999999</v>
@@ -6125,37 +6125,37 @@
         <v>57.5</v>
       </c>
       <c r="M59">
-        <v>68.53901160000001</v>
+        <v>69.74145040000001</v>
       </c>
       <c r="N59">
-        <v>-11.03901160000001</v>
+        <v>-12.24145040000001</v>
       </c>
       <c r="O59">
-        <v>-2.925338074000003</v>
+        <v>-3.243984356000002</v>
       </c>
       <c r="P59">
-        <v>-8.113673526000007</v>
+        <v>-8.997466044000003</v>
       </c>
       <c r="Q59">
-        <v>0.8863264739999934</v>
+        <v>0.002533955999997062</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09214338064722911</v>
+        <v>0.09324679447216314</v>
       </c>
       <c r="T59">
-        <v>1.070285927187739</v>
+        <v>1.095768925454114</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2223186422489933</v>
+        <v>0.2184855622102175</v>
       </c>
       <c r="W59">
-        <v>0.1141636233178478</v>
+        <v>0.1147263194675401</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8389382726377104</v>
+        <v>0.8244738196611981</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1057049189694818</v>
+        <v>0.1067149189694818</v>
       </c>
       <c r="C60">
-        <v>-33.78169478850157</v>
+        <v>-46.61206607382081</v>
       </c>
       <c r="D60">
-        <v>431.9363052114983</v>
+        <v>427.2969339261791</v>
       </c>
       <c r="E60">
-        <v>13.178</v>
+        <v>21.36900000000003</v>
       </c>
       <c r="F60">
-        <v>475.0779999999999</v>
+        <v>483.2689999999999</v>
       </c>
       <c r="G60">
         <v>9.359999999999999</v>
@@ -6207,37 +6207,37 @@
         <v>57.5</v>
       </c>
       <c r="M60">
-        <v>69.74145039999999</v>
+        <v>70.9438892</v>
       </c>
       <c r="N60">
-        <v>-12.24145039999999</v>
+        <v>-13.4438892</v>
       </c>
       <c r="O60">
-        <v>-3.243984355999998</v>
+        <v>-3.562630638</v>
       </c>
       <c r="P60">
-        <v>-8.997466043999992</v>
+        <v>-9.881258562000001</v>
       </c>
       <c r="Q60">
-        <v>0.00253395600000772</v>
+        <v>-0.8812585620000011</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09324679447216314</v>
+        <v>0.09440403336172808</v>
       </c>
       <c r="T60">
-        <v>1.095768925454114</v>
+        <v>1.122494996806653</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2184855622102176</v>
+        <v>0.2147824170880105</v>
       </c>
       <c r="W60">
-        <v>0.1147263194675401</v>
+        <v>0.1152699411714801</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8244738196611983</v>
+        <v>0.8104996871245678</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1067149189694818</v>
+        <v>0.1409025691016748</v>
       </c>
       <c r="C61">
-        <v>-46.61206607382081</v>
+        <v>-168.7335218801687</v>
       </c>
       <c r="D61">
-        <v>427.2969339261791</v>
+        <v>313.3664781198312</v>
       </c>
       <c r="E61">
-        <v>21.36900000000003</v>
+        <v>29.56</v>
       </c>
       <c r="F61">
-        <v>483.2689999999999</v>
+        <v>491.4599999999999</v>
       </c>
       <c r="G61">
         <v>9.359999999999999</v>
@@ -6289,45 +6289,45 @@
         <v>57.5</v>
       </c>
       <c r="M61">
-        <v>70.9438892</v>
+        <v>98.68516799999999</v>
       </c>
       <c r="N61">
-        <v>-13.4438892</v>
+        <v>-41.18516799999999</v>
       </c>
       <c r="O61">
-        <v>-3.562630638</v>
+        <v>-10.91406952</v>
       </c>
       <c r="P61">
-        <v>-9.881258562000001</v>
+        <v>-30.27109847999999</v>
       </c>
       <c r="Q61">
-        <v>-0.8812585620000011</v>
+        <v>-21.27109847999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09440403336172808</v>
+        <v>0.09756325952625401</v>
       </c>
       <c r="T61">
-        <v>1.122494996806653</v>
+        <v>1.195456340098245</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.2147824170880105</v>
+        <v>0.1544051685659592</v>
       </c>
       <c r="W61">
-        <v>0.1152699411714801</v>
+        <v>0.1697954421519554</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8104996871245678</v>
+        <v>0.5826610134564498</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1409025691016748</v>
+        <v>0.1424525691016749</v>
       </c>
       <c r="C62">
-        <v>-168.7335218801687</v>
+        <v>-180.6674074613964</v>
       </c>
       <c r="D62">
-        <v>313.3664781198312</v>
+        <v>309.6235925386036</v>
       </c>
       <c r="E62">
-        <v>29.56</v>
+        <v>37.75100000000003</v>
       </c>
       <c r="F62">
-        <v>491.4599999999999</v>
+        <v>499.651</v>
       </c>
       <c r="G62">
         <v>9.359999999999999</v>
@@ -6371,37 +6371,37 @@
         <v>57.5</v>
       </c>
       <c r="M62">
-        <v>98.68516799999999</v>
+        <v>100.3299208</v>
       </c>
       <c r="N62">
-        <v>-41.18516799999999</v>
+        <v>-42.8299208</v>
       </c>
       <c r="O62">
-        <v>-10.91406952</v>
+        <v>-11.349929012</v>
       </c>
       <c r="P62">
-        <v>-30.27109847999999</v>
+        <v>-31.479991788</v>
       </c>
       <c r="Q62">
-        <v>-21.27109847999999</v>
+        <v>-22.479991788</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09756325952625401</v>
+        <v>0.09889052259102976</v>
       </c>
       <c r="T62">
-        <v>1.195456340098245</v>
+        <v>1.226109066767431</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1544051685659592</v>
+        <v>0.1518739362943861</v>
       </c>
       <c r="W62">
-        <v>0.1697954421519554</v>
+        <v>0.1703037135920873</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5826610134564498</v>
+        <v>0.573109193563721</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1424525691016749</v>
+        <v>0.1440025691016749</v>
       </c>
       <c r="C63">
-        <v>-180.6674074613964</v>
+        <v>-192.5129374525483</v>
       </c>
       <c r="D63">
-        <v>309.6235925386036</v>
+        <v>305.9690625474516</v>
       </c>
       <c r="E63">
-        <v>37.75100000000003</v>
+        <v>45.94200000000001</v>
       </c>
       <c r="F63">
-        <v>499.651</v>
+        <v>507.8419999999999</v>
       </c>
       <c r="G63">
         <v>9.359999999999999</v>
@@ -6453,37 +6453,37 @@
         <v>57.5</v>
       </c>
       <c r="M63">
-        <v>100.3299208</v>
+        <v>101.9746736</v>
       </c>
       <c r="N63">
-        <v>-42.8299208</v>
+        <v>-44.47467359999999</v>
       </c>
       <c r="O63">
-        <v>-11.349929012</v>
+        <v>-11.785788504</v>
       </c>
       <c r="P63">
-        <v>-31.479991788</v>
+        <v>-32.68888509599999</v>
       </c>
       <c r="Q63">
-        <v>-22.479991788</v>
+        <v>-23.68888509599999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09889052259102976</v>
+        <v>0.1002876416065832</v>
       </c>
       <c r="T63">
-        <v>1.226109066767431</v>
+        <v>1.258375094840258</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1518739362943861</v>
+        <v>0.1494243566767347</v>
       </c>
       <c r="W63">
-        <v>0.1703037135920873</v>
+        <v>0.1707955891793117</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.573109193563721</v>
+        <v>0.5638654968933385</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1440025691016749</v>
+        <v>0.1455525691016749</v>
       </c>
       <c r="C64">
-        <v>-192.5129374525483</v>
+        <v>-204.2732039765395</v>
       </c>
       <c r="D64">
-        <v>305.9690625474516</v>
+        <v>302.3997960234604</v>
       </c>
       <c r="E64">
-        <v>45.94200000000001</v>
+        <v>54.13299999999998</v>
       </c>
       <c r="F64">
-        <v>507.8419999999999</v>
+        <v>516.0329999999999</v>
       </c>
       <c r="G64">
         <v>9.359999999999999</v>
@@ -6535,37 +6535,37 @@
         <v>57.5</v>
       </c>
       <c r="M64">
-        <v>101.9746736</v>
+        <v>103.6194264</v>
       </c>
       <c r="N64">
-        <v>-44.47467359999999</v>
+        <v>-46.11942639999998</v>
       </c>
       <c r="O64">
-        <v>-11.785788504</v>
+        <v>-12.221647996</v>
       </c>
       <c r="P64">
-        <v>-32.68888509599999</v>
+        <v>-33.89777840399999</v>
       </c>
       <c r="Q64">
-        <v>-23.68888509599999</v>
+        <v>-24.89777840399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1002876416065832</v>
+        <v>0.1017602805689233</v>
       </c>
       <c r="T64">
-        <v>1.258375094840258</v>
+        <v>1.292385232538644</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1494243566767347</v>
+        <v>0.1470525414913897</v>
       </c>
       <c r="W64">
-        <v>0.1707955891793117</v>
+        <v>0.171271849668529</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5638654968933385</v>
+        <v>0.5549152509109045</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1455525691016749</v>
+        <v>0.1471025691016749</v>
       </c>
       <c r="C65">
-        <v>-204.2732039765395</v>
+        <v>-215.9511565360051</v>
       </c>
       <c r="D65">
-        <v>302.3997960234604</v>
+        <v>298.9128434639948</v>
       </c>
       <c r="E65">
-        <v>54.13299999999998</v>
+        <v>62.32400000000001</v>
       </c>
       <c r="F65">
-        <v>516.0329999999999</v>
+        <v>524.2239999999999</v>
       </c>
       <c r="G65">
         <v>9.359999999999999</v>
@@ -6617,37 +6617,37 @@
         <v>57.5</v>
       </c>
       <c r="M65">
-        <v>103.6194264</v>
+        <v>105.2641792</v>
       </c>
       <c r="N65">
-        <v>-46.11942639999998</v>
+        <v>-47.76417919999999</v>
       </c>
       <c r="O65">
-        <v>-12.221647996</v>
+        <v>-12.657507488</v>
       </c>
       <c r="P65">
-        <v>-33.89777840399999</v>
+        <v>-35.10667171199999</v>
       </c>
       <c r="Q65">
-        <v>-24.89777840399999</v>
+        <v>-26.10667171199999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1017602805689233</v>
+        <v>0.1033147328069489</v>
       </c>
       <c r="T65">
-        <v>1.292385232538644</v>
+        <v>1.328284822331384</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1470525414913897</v>
+        <v>0.1447548455305868</v>
       </c>
       <c r="W65">
-        <v>0.171271849668529</v>
+        <v>0.1717332270174582</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5549152509109045</v>
+        <v>0.5462447001154216</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1471025691016749</v>
+        <v>0.1486525691016748</v>
       </c>
       <c r="C66">
-        <v>-215.9511565360051</v>
+        <v>-227.5496101422908</v>
       </c>
       <c r="D66">
-        <v>298.9128434639948</v>
+        <v>295.5053898577092</v>
       </c>
       <c r="E66">
-        <v>62.32400000000001</v>
+        <v>70.51500000000004</v>
       </c>
       <c r="F66">
-        <v>524.2239999999999</v>
+        <v>532.415</v>
       </c>
       <c r="G66">
         <v>9.359999999999999</v>
@@ -6699,37 +6699,37 @@
         <v>57.5</v>
       </c>
       <c r="M66">
-        <v>105.2641792</v>
+        <v>106.908932</v>
       </c>
       <c r="N66">
-        <v>-47.76417919999999</v>
+        <v>-49.40893199999999</v>
       </c>
       <c r="O66">
-        <v>-12.657507488</v>
+        <v>-13.09336698</v>
       </c>
       <c r="P66">
-        <v>-35.10667171199999</v>
+        <v>-36.31556501999999</v>
       </c>
       <c r="Q66">
-        <v>-26.10667171199999</v>
+        <v>-27.31556501999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1033147328069489</v>
+        <v>0.1049580108871475</v>
       </c>
       <c r="T66">
-        <v>1.328284822331384</v>
+        <v>1.366235817255137</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1447548455305868</v>
+        <v>0.1425278479070392</v>
       </c>
       <c r="W66">
-        <v>0.1717332270174582</v>
+        <v>0.1721804081402665</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5462447001154216</v>
+        <v>0.5378409354982613</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1486525691016748</v>
+        <v>0.1502025691016748</v>
       </c>
       <c r="C67">
-        <v>-227.5496101422908</v>
+        <v>-239.0712528947137</v>
       </c>
       <c r="D67">
-        <v>295.5053898577092</v>
+        <v>292.1747471052863</v>
       </c>
       <c r="E67">
-        <v>70.51500000000004</v>
+        <v>78.70600000000007</v>
       </c>
       <c r="F67">
-        <v>532.415</v>
+        <v>540.606</v>
       </c>
       <c r="G67">
         <v>9.359999999999999</v>
@@ -6781,37 +6781,37 @@
         <v>57.5</v>
       </c>
       <c r="M67">
-        <v>106.908932</v>
+        <v>108.5536848</v>
       </c>
       <c r="N67">
-        <v>-49.40893199999999</v>
+        <v>-51.0536848</v>
       </c>
       <c r="O67">
-        <v>-13.09336698</v>
+        <v>-13.529226472</v>
       </c>
       <c r="P67">
-        <v>-36.31556501999999</v>
+        <v>-37.52445832799999</v>
       </c>
       <c r="Q67">
-        <v>-27.31556501999999</v>
+        <v>-28.52445832799999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1049580108871475</v>
+        <v>0.1066979523838283</v>
       </c>
       <c r="T67">
-        <v>1.366235817255137</v>
+        <v>1.406419223644994</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1425278479070392</v>
+        <v>0.1403683350599629</v>
       </c>
       <c r="W67">
-        <v>0.1721804081402665</v>
+        <v>0.1726140383199594</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5378409354982613</v>
+        <v>0.5296918304149543</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1502025691016748</v>
+        <v>0.1517525691016749</v>
       </c>
       <c r="C68">
-        <v>-239.0712528947137</v>
+        <v>-250.5186530529799</v>
       </c>
       <c r="D68">
-        <v>292.1747471052863</v>
+        <v>288.9183469470201</v>
       </c>
       <c r="E68">
-        <v>78.70600000000007</v>
+        <v>86.89700000000011</v>
       </c>
       <c r="F68">
-        <v>540.606</v>
+        <v>548.797</v>
       </c>
       <c r="G68">
         <v>9.359999999999999</v>
@@ -6863,37 +6863,37 @@
         <v>57.5</v>
       </c>
       <c r="M68">
-        <v>108.5536848</v>
+        <v>110.1984376</v>
       </c>
       <c r="N68">
-        <v>-51.0536848</v>
+        <v>-52.69843760000001</v>
       </c>
       <c r="O68">
-        <v>-13.529226472</v>
+        <v>-13.965085964</v>
       </c>
       <c r="P68">
-        <v>-37.52445832799999</v>
+        <v>-38.733351636</v>
       </c>
       <c r="Q68">
-        <v>-28.52445832799999</v>
+        <v>-29.733351636</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1066979523838283</v>
+        <v>0.1085433448803079</v>
       </c>
       <c r="T68">
-        <v>1.406419223644994</v>
+        <v>1.449037987997873</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1403683350599629</v>
+        <v>0.1382732852829485</v>
       </c>
       <c r="W68">
-        <v>0.1726140383199594</v>
+        <v>0.173034724315184</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5296918304149543</v>
+        <v>0.5217859821998057</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1517525691016749</v>
+        <v>0.1533025691016749</v>
       </c>
       <c r="C69">
-        <v>-250.5186530529799</v>
+        <v>-261.8942656418649</v>
       </c>
       <c r="D69">
-        <v>288.9183469470201</v>
+        <v>285.7337343581351</v>
       </c>
       <c r="E69">
-        <v>86.89700000000011</v>
+        <v>95.08800000000002</v>
       </c>
       <c r="F69">
-        <v>548.797</v>
+        <v>556.9879999999999</v>
       </c>
       <c r="G69">
         <v>9.359999999999999</v>
@@ -6945,37 +6945,37 @@
         <v>57.5</v>
       </c>
       <c r="M69">
-        <v>110.1984376</v>
+        <v>111.8431904</v>
       </c>
       <c r="N69">
-        <v>-52.69843760000001</v>
+        <v>-54.3431904</v>
       </c>
       <c r="O69">
-        <v>-13.965085964</v>
+        <v>-14.400945456</v>
       </c>
       <c r="P69">
-        <v>-38.733351636</v>
+        <v>-39.942244944</v>
       </c>
       <c r="Q69">
-        <v>-29.733351636</v>
+        <v>-30.942244944</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1085433448803079</v>
+        <v>0.1105040744078175</v>
       </c>
       <c r="T69">
-        <v>1.449037987997873</v>
+        <v>1.494320425122806</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1382732852829485</v>
+        <v>0.1362398546170228</v>
       </c>
       <c r="W69">
-        <v>0.173034724315184</v>
+        <v>0.1734430371929018</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5217859821998057</v>
+        <v>0.5141126589321615</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1533025691016749</v>
+        <v>0.1548525691016749</v>
       </c>
       <c r="C70">
-        <v>-261.8942656418649</v>
+        <v>-273.2004386238565</v>
       </c>
       <c r="D70">
-        <v>285.7337343581351</v>
+        <v>282.6185613761435</v>
       </c>
       <c r="E70">
-        <v>95.08800000000002</v>
+        <v>103.2790000000001</v>
       </c>
       <c r="F70">
-        <v>556.9879999999999</v>
+        <v>565.179</v>
       </c>
       <c r="G70">
         <v>9.359999999999999</v>
@@ -7027,37 +7027,37 @@
         <v>57.5</v>
       </c>
       <c r="M70">
-        <v>111.8431904</v>
+        <v>113.4879432</v>
       </c>
       <c r="N70">
-        <v>-54.3431904</v>
+        <v>-55.9879432</v>
       </c>
       <c r="O70">
-        <v>-14.400945456</v>
+        <v>-14.836804948</v>
       </c>
       <c r="P70">
-        <v>-39.942244944</v>
+        <v>-41.151138252</v>
       </c>
       <c r="Q70">
-        <v>-30.942244944</v>
+        <v>-32.151138252</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1105040744078175</v>
+        <v>0.1125913026145213</v>
       </c>
       <c r="T70">
-        <v>1.494320425122806</v>
+        <v>1.542524309804188</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1362398546170228</v>
+        <v>0.1342653639703993</v>
       </c>
       <c r="W70">
-        <v>0.1734430371929018</v>
+        <v>0.1738395149147438</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5141126589321615</v>
+        <v>0.5066617508316954</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1548525691016749</v>
+        <v>0.1812163603229867</v>
       </c>
       <c r="C71">
-        <v>-273.2004386238565</v>
+        <v>-325.6012795970052</v>
       </c>
       <c r="D71">
-        <v>282.6185613761435</v>
+        <v>238.4087204029948</v>
       </c>
       <c r="E71">
-        <v>103.2790000000001</v>
+        <v>111.4700000000001</v>
       </c>
       <c r="F71">
-        <v>565.179</v>
+        <v>573.37</v>
       </c>
       <c r="G71">
         <v>9.359999999999999</v>
@@ -7109,45 +7109,45 @@
         <v>57.5</v>
       </c>
       <c r="M71">
-        <v>113.4879432</v>
+        <v>135.200646</v>
       </c>
       <c r="N71">
-        <v>-55.9879432</v>
+        <v>-77.70064600000001</v>
       </c>
       <c r="O71">
-        <v>-14.836804948</v>
+        <v>-20.59067119</v>
       </c>
       <c r="P71">
-        <v>-41.151138252</v>
+        <v>-57.10997481</v>
       </c>
       <c r="Q71">
-        <v>-32.151138252</v>
+        <v>-48.10997481</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1125913026145213</v>
+        <v>0.1158636501060449</v>
       </c>
       <c r="T71">
-        <v>1.542524309804188</v>
+        <v>1.618098154874016</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1342653639703993</v>
+        <v>0.1127028638605765</v>
       </c>
       <c r="W71">
-        <v>0.1738395149147438</v>
+        <v>0.2092246647016761</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5066617508316954</v>
+        <v>0.425293825888968</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1812163603229867</v>
+        <v>0.1831163603229867</v>
       </c>
       <c r="C72">
-        <v>-325.6012795970052</v>
+        <v>-336.4500499954455</v>
       </c>
       <c r="D72">
-        <v>238.4087204029948</v>
+        <v>235.7509500045546</v>
       </c>
       <c r="E72">
-        <v>111.4700000000001</v>
+        <v>119.6610000000001</v>
       </c>
       <c r="F72">
-        <v>573.37</v>
+        <v>581.561</v>
       </c>
       <c r="G72">
         <v>9.359999999999999</v>
@@ -7191,37 +7191,37 @@
         <v>57.5</v>
       </c>
       <c r="M72">
-        <v>135.200646</v>
+        <v>137.1320838</v>
       </c>
       <c r="N72">
-        <v>-77.70064600000001</v>
+        <v>-79.6320838</v>
       </c>
       <c r="O72">
-        <v>-20.59067119</v>
+        <v>-21.102502207</v>
       </c>
       <c r="P72">
-        <v>-57.10997481</v>
+        <v>-58.529581593</v>
       </c>
       <c r="Q72">
-        <v>-48.10997481</v>
+        <v>-49.529581593</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1158636501060449</v>
+        <v>0.1182796380407361</v>
       </c>
       <c r="T72">
-        <v>1.618098154874016</v>
+        <v>1.67389464297312</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1127028638605765</v>
+        <v>0.1111154995808501</v>
       </c>
       <c r="W72">
-        <v>0.2092246647016761</v>
+        <v>0.2095989651988356</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.425293825888968</v>
+        <v>0.4193037720032079</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1831163603229867</v>
+        <v>0.1850163603229867</v>
       </c>
       <c r="C73">
-        <v>-336.4500499954453</v>
+        <v>-347.2402162845601</v>
       </c>
       <c r="D73">
-        <v>235.7509500045546</v>
+        <v>233.1517837154399</v>
       </c>
       <c r="E73">
-        <v>119.661</v>
+        <v>127.852</v>
       </c>
       <c r="F73">
-        <v>581.5609999999999</v>
+        <v>589.752</v>
       </c>
       <c r="G73">
         <v>9.359999999999999</v>
@@ -7273,37 +7273,37 @@
         <v>57.5</v>
       </c>
       <c r="M73">
-        <v>137.1320838</v>
+        <v>139.0635216</v>
       </c>
       <c r="N73">
-        <v>-79.63208379999998</v>
+        <v>-81.5635216</v>
       </c>
       <c r="O73">
-        <v>-21.10250220699999</v>
+        <v>-21.614333224</v>
       </c>
       <c r="P73">
-        <v>-58.52958159299998</v>
+        <v>-59.949188376</v>
       </c>
       <c r="Q73">
-        <v>-49.52958159299998</v>
+        <v>-50.949188376</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1182796380407361</v>
+        <v>0.1208681965421909</v>
       </c>
       <c r="T73">
-        <v>1.673894642973119</v>
+        <v>1.733676594507874</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1111154995808501</v>
+        <v>0.1095722287533383</v>
       </c>
       <c r="W73">
-        <v>0.2095989651988356</v>
+        <v>0.2099628684599628</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.419303772003208</v>
+        <v>0.4134801085031633</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1850163603229867</v>
+        <v>0.1869163603229867</v>
       </c>
       <c r="C74">
-        <v>-347.2402162845601</v>
+        <v>-357.9736956670055</v>
       </c>
       <c r="D74">
-        <v>233.1517837154399</v>
+        <v>230.6093043329944</v>
       </c>
       <c r="E74">
-        <v>127.852</v>
+        <v>136.0429999999999</v>
       </c>
       <c r="F74">
-        <v>589.752</v>
+        <v>597.9429999999999</v>
       </c>
       <c r="G74">
         <v>9.359999999999999</v>
@@ -7355,37 +7355,37 @@
         <v>57.5</v>
       </c>
       <c r="M74">
-        <v>139.0635216</v>
+        <v>140.9949594</v>
       </c>
       <c r="N74">
-        <v>-81.5635216</v>
+        <v>-83.49495939999997</v>
       </c>
       <c r="O74">
-        <v>-21.614333224</v>
+        <v>-22.12616424099999</v>
       </c>
       <c r="P74">
-        <v>-59.949188376</v>
+        <v>-61.36879515899997</v>
       </c>
       <c r="Q74">
-        <v>-50.949188376</v>
+        <v>-52.36879515899997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1208681965421909</v>
+        <v>0.1236485001178276</v>
       </c>
       <c r="T74">
-        <v>1.733676594507874</v>
+        <v>1.797886838748906</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1095722287533383</v>
+        <v>0.1080712393183611</v>
       </c>
       <c r="W74">
-        <v>0.2099628684599628</v>
+        <v>0.2103168017687305</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4134801085031633</v>
+        <v>0.4078159974277776</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1869163603229867</v>
+        <v>0.1888163603229867</v>
       </c>
       <c r="C75">
-        <v>-357.9736956670055</v>
+        <v>-368.6523226205016</v>
       </c>
       <c r="D75">
-        <v>230.6093043329944</v>
+        <v>228.1216773794983</v>
       </c>
       <c r="E75">
-        <v>136.0429999999999</v>
+        <v>144.234</v>
       </c>
       <c r="F75">
-        <v>597.9429999999999</v>
+        <v>606.1339999999999</v>
       </c>
       <c r="G75">
         <v>9.359999999999999</v>
@@ -7437,37 +7437,37 @@
         <v>57.5</v>
       </c>
       <c r="M75">
-        <v>140.9949594</v>
+        <v>142.9263972</v>
       </c>
       <c r="N75">
-        <v>-83.49495939999997</v>
+        <v>-85.42639719999997</v>
       </c>
       <c r="O75">
-        <v>-22.12616424099999</v>
+        <v>-22.63799525799999</v>
       </c>
       <c r="P75">
-        <v>-61.36879515899997</v>
+        <v>-62.78840194199998</v>
       </c>
       <c r="Q75">
-        <v>-52.36879515899997</v>
+        <v>-53.78840194199998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1236485001178276</v>
+        <v>0.1266426731992825</v>
       </c>
       <c r="T75">
-        <v>1.797886838748906</v>
+        <v>1.867036332546941</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1080712393183611</v>
+        <v>0.1066108171654103</v>
       </c>
       <c r="W75">
-        <v>0.2103168017687305</v>
+        <v>0.2106611693123963</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4078159974277776</v>
+        <v>0.4023049704355104</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1888163603229867</v>
+        <v>0.1907163603229867</v>
       </c>
       <c r="C76">
-        <v>-368.6523226205016</v>
+        <v>-379.2778533120645</v>
       </c>
       <c r="D76">
-        <v>228.1216773794983</v>
+        <v>225.6871466879355</v>
       </c>
       <c r="E76">
-        <v>144.234</v>
+        <v>152.425</v>
       </c>
       <c r="F76">
-        <v>606.1339999999999</v>
+        <v>614.3249999999999</v>
       </c>
       <c r="G76">
         <v>9.359999999999999</v>
@@ -7519,37 +7519,37 @@
         <v>57.5</v>
       </c>
       <c r="M76">
-        <v>142.9263972</v>
+        <v>144.857835</v>
       </c>
       <c r="N76">
-        <v>-85.42639719999997</v>
+        <v>-87.35783499999999</v>
       </c>
       <c r="O76">
-        <v>-22.63799525799999</v>
+        <v>-23.149826275</v>
       </c>
       <c r="P76">
-        <v>-62.78840194199998</v>
+        <v>-64.208008725</v>
       </c>
       <c r="Q76">
-        <v>-53.78840194199998</v>
+        <v>-55.208008725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1266426731992825</v>
+        <v>0.1298763801272539</v>
       </c>
       <c r="T76">
-        <v>1.867036332546941</v>
+        <v>1.941717785848819</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1066108171654103</v>
+        <v>0.1051893396032048</v>
       </c>
       <c r="W76">
-        <v>0.2106611693123963</v>
+        <v>0.2109963537215643</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4023049704355104</v>
+        <v>0.3969409041630368</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1907163603229867</v>
+        <v>0.1926163603229867</v>
       </c>
       <c r="C77">
-        <v>-379.2778533120645</v>
+        <v>-389.8519697325671</v>
       </c>
       <c r="D77">
-        <v>225.6871466879355</v>
+        <v>223.3040302674329</v>
       </c>
       <c r="E77">
-        <v>152.425</v>
+        <v>160.616</v>
       </c>
       <c r="F77">
-        <v>614.3249999999999</v>
+        <v>622.516</v>
       </c>
       <c r="G77">
         <v>9.359999999999999</v>
@@ -7601,37 +7601,37 @@
         <v>57.5</v>
       </c>
       <c r="M77">
-        <v>144.857835</v>
+        <v>146.7892728</v>
       </c>
       <c r="N77">
-        <v>-87.35783499999999</v>
+        <v>-89.28927279999999</v>
       </c>
       <c r="O77">
-        <v>-23.149826275</v>
+        <v>-23.661657292</v>
       </c>
       <c r="P77">
-        <v>-64.208008725</v>
+        <v>-65.62761550799999</v>
       </c>
       <c r="Q77">
-        <v>-55.208008725</v>
+        <v>-56.62761550799999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1298763801272539</v>
+        <v>0.1333795626325561</v>
       </c>
       <c r="T77">
-        <v>1.941717785848819</v>
+        <v>2.02262269359252</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1051893396032048</v>
+        <v>0.1038052693452679</v>
       </c>
       <c r="W77">
-        <v>0.2109963537215643</v>
+        <v>0.2113227174883858</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3969409041630368</v>
+        <v>0.3917179975293127</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1926163603229867</v>
+        <v>0.1945163603229867</v>
       </c>
       <c r="C78">
-        <v>-389.8519697325671</v>
+        <v>-400.3762835720908</v>
       </c>
       <c r="D78">
-        <v>223.3040302674329</v>
+        <v>220.9707164279092</v>
       </c>
       <c r="E78">
-        <v>160.616</v>
+        <v>168.8070000000001</v>
       </c>
       <c r="F78">
-        <v>622.516</v>
+        <v>630.707</v>
       </c>
       <c r="G78">
         <v>9.359999999999999</v>
@@ -7683,37 +7683,37 @@
         <v>57.5</v>
       </c>
       <c r="M78">
-        <v>146.7892728</v>
+        <v>148.7207106</v>
       </c>
       <c r="N78">
-        <v>-89.28927279999999</v>
+        <v>-91.22071060000002</v>
       </c>
       <c r="O78">
-        <v>-23.661657292</v>
+        <v>-24.17348830900001</v>
       </c>
       <c r="P78">
-        <v>-65.62761550799999</v>
+        <v>-67.04722229100001</v>
       </c>
       <c r="Q78">
-        <v>-56.62761550799999</v>
+        <v>-58.04722229100001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1333795626325561</v>
+        <v>0.1371873697035368</v>
       </c>
       <c r="T78">
-        <v>2.02262269359252</v>
+        <v>2.110562810705238</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1038052693452679</v>
+        <v>0.1024571489641605</v>
       </c>
       <c r="W78">
-        <v>0.2113227174883858</v>
+        <v>0.211640604274251</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3917179975293127</v>
+        <v>0.3866307508081527</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1945163603229867</v>
+        <v>0.1964163603229867</v>
       </c>
       <c r="C79">
-        <v>-400.3762835720908</v>
+        <v>-410.8523398548233</v>
       </c>
       <c r="D79">
-        <v>220.9707164279092</v>
+        <v>218.6856601451766</v>
       </c>
       <c r="E79">
-        <v>168.8070000000001</v>
+        <v>176.998</v>
       </c>
       <c r="F79">
-        <v>630.707</v>
+        <v>638.8979999999999</v>
       </c>
       <c r="G79">
         <v>9.359999999999999</v>
@@ -7765,37 +7765,37 @@
         <v>57.5</v>
       </c>
       <c r="M79">
-        <v>148.7207106</v>
+        <v>150.6521484</v>
       </c>
       <c r="N79">
-        <v>-91.22071060000002</v>
+        <v>-93.15214839999999</v>
       </c>
       <c r="O79">
-        <v>-24.17348830900001</v>
+        <v>-24.685319326</v>
       </c>
       <c r="P79">
-        <v>-67.04722229100001</v>
+        <v>-68.46682907399999</v>
       </c>
       <c r="Q79">
-        <v>-58.04722229100001</v>
+        <v>-59.46682907399999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1371873697035368</v>
+        <v>0.1413413410536976</v>
       </c>
       <c r="T79">
-        <v>2.110562810705238</v>
+        <v>2.206497483919112</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1024571489641605</v>
+        <v>0.1011435957723123</v>
       </c>
       <c r="W79">
-        <v>0.211640604274251</v>
+        <v>0.2119503401168888</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3866307508081527</v>
+        <v>0.3816739463106124</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1964163603229867</v>
+        <v>0.1983163603229867</v>
       </c>
       <c r="C80">
-        <v>-410.8523398548233</v>
+        <v>-421.2816203507367</v>
       </c>
       <c r="D80">
-        <v>218.6856601451766</v>
+        <v>216.4473796492632</v>
       </c>
       <c r="E80">
-        <v>176.998</v>
+        <v>185.189</v>
       </c>
       <c r="F80">
-        <v>638.8979999999999</v>
+        <v>647.0889999999999</v>
       </c>
       <c r="G80">
         <v>9.359999999999999</v>
@@ -7847,37 +7847,37 @@
         <v>57.5</v>
       </c>
       <c r="M80">
-        <v>150.6521484</v>
+        <v>152.5835862</v>
       </c>
       <c r="N80">
-        <v>-93.15214839999999</v>
+        <v>-95.08358619999998</v>
       </c>
       <c r="O80">
-        <v>-24.685319326</v>
+        <v>-25.197150343</v>
       </c>
       <c r="P80">
-        <v>-68.46682907399999</v>
+        <v>-69.88643585699998</v>
       </c>
       <c r="Q80">
-        <v>-59.46682907399999</v>
+        <v>-60.88643585699998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1413413410536976</v>
+        <v>0.1458909287229213</v>
       </c>
       <c r="T80">
-        <v>2.206497483919112</v>
+        <v>2.311568792677165</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1011435957723123</v>
+        <v>0.09986329709165009</v>
       </c>
       <c r="W80">
-        <v>0.2119503401168888</v>
+        <v>0.2122522345457889</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3816739463106124</v>
+        <v>0.3768426305345287</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1983163603229867</v>
+        <v>0.2002163603229867</v>
       </c>
       <c r="C81">
-        <v>-421.2816203507367</v>
+        <v>-431.6655467798715</v>
       </c>
       <c r="D81">
-        <v>216.4473796492632</v>
+        <v>214.2544532201285</v>
       </c>
       <c r="E81">
-        <v>185.189</v>
+        <v>193.3800000000001</v>
       </c>
       <c r="F81">
-        <v>647.0889999999999</v>
+        <v>655.28</v>
       </c>
       <c r="G81">
         <v>9.359999999999999</v>
@@ -7929,37 +7929,37 @@
         <v>57.5</v>
       </c>
       <c r="M81">
-        <v>152.5835862</v>
+        <v>154.515024</v>
       </c>
       <c r="N81">
-        <v>-95.08358619999998</v>
+        <v>-97.01502400000001</v>
       </c>
       <c r="O81">
-        <v>-25.197150343</v>
+        <v>-25.70898136</v>
       </c>
       <c r="P81">
-        <v>-69.88643585699998</v>
+        <v>-71.30604264000002</v>
       </c>
       <c r="Q81">
-        <v>-60.88643585699998</v>
+        <v>-62.30604264000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1458909287229213</v>
+        <v>0.1508954751590673</v>
       </c>
       <c r="T81">
-        <v>2.311568792677165</v>
+        <v>2.427147232311024</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09986329709165009</v>
+        <v>0.09861500587800445</v>
       </c>
       <c r="W81">
-        <v>0.2122522345457889</v>
+        <v>0.2125465816139666</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3768426305345287</v>
+        <v>0.3721320976528469</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2002163603229867</v>
+        <v>0.2021163603229867</v>
       </c>
       <c r="C82">
-        <v>-431.6655467798715</v>
+        <v>-442.0054838237934</v>
       </c>
       <c r="D82">
-        <v>214.2544532201285</v>
+        <v>212.1055161762066</v>
       </c>
       <c r="E82">
-        <v>193.3800000000001</v>
+        <v>201.5710000000001</v>
       </c>
       <c r="F82">
-        <v>655.28</v>
+        <v>663.471</v>
       </c>
       <c r="G82">
         <v>9.359999999999999</v>
@@ -8011,37 +8011,37 @@
         <v>57.5</v>
       </c>
       <c r="M82">
-        <v>154.515024</v>
+        <v>156.4464618</v>
       </c>
       <c r="N82">
-        <v>-97.01502400000001</v>
+        <v>-98.94646180000001</v>
       </c>
       <c r="O82">
-        <v>-25.70898136</v>
+        <v>-26.22081237700001</v>
       </c>
       <c r="P82">
-        <v>-71.30604264000002</v>
+        <v>-72.72564942300001</v>
       </c>
       <c r="Q82">
-        <v>-62.30604264000002</v>
+        <v>-63.72564942300001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1508954751590673</v>
+        <v>0.156426815956913</v>
       </c>
       <c r="T82">
-        <v>2.427147232311024</v>
+        <v>2.554891823485288</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09861500587800445</v>
+        <v>0.09739753666963404</v>
       </c>
       <c r="W82">
-        <v>0.2125465816139666</v>
+        <v>0.2128336608533003</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3721320976528469</v>
+        <v>0.367537874225034</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2021163603229867</v>
+        <v>0.2040163603229867</v>
       </c>
       <c r="C83">
-        <v>-442.0054838237934</v>
+        <v>-452.3027419576195</v>
       </c>
       <c r="D83">
-        <v>212.1055161762066</v>
+        <v>209.9992580423804</v>
       </c>
       <c r="E83">
-        <v>201.5710000000001</v>
+        <v>209.762</v>
       </c>
       <c r="F83">
-        <v>663.471</v>
+        <v>671.6619999999999</v>
       </c>
       <c r="G83">
         <v>9.359999999999999</v>
@@ -8093,37 +8093,37 @@
         <v>57.5</v>
       </c>
       <c r="M83">
-        <v>156.4464618</v>
+        <v>158.3778996</v>
       </c>
       <c r="N83">
-        <v>-98.94646180000001</v>
+        <v>-100.8778996</v>
       </c>
       <c r="O83">
-        <v>-26.22081237700001</v>
+        <v>-26.732643394</v>
       </c>
       <c r="P83">
-        <v>-72.72564942300001</v>
+        <v>-74.14525620599998</v>
       </c>
       <c r="Q83">
-        <v>-63.72564942300001</v>
+        <v>-65.14525620599998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.156426815956913</v>
+        <v>0.1625727501767415</v>
       </c>
       <c r="T83">
-        <v>2.554891823485288</v>
+        <v>2.69683025812336</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09739753666963404</v>
+        <v>0.09620976183219949</v>
       </c>
       <c r="W83">
-        <v>0.2128336608533003</v>
+        <v>0.2131137381599674</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.367537874225034</v>
+        <v>0.3630557050271679</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2040163603229867</v>
+        <v>0.2059163603229867</v>
       </c>
       <c r="C84">
-        <v>-452.3027419576195</v>
+        <v>-462.5585801149707</v>
       </c>
       <c r="D84">
-        <v>209.9992580423804</v>
+        <v>207.9344198850293</v>
       </c>
       <c r="E84">
-        <v>209.762</v>
+        <v>217.953</v>
       </c>
       <c r="F84">
-        <v>671.6619999999999</v>
+        <v>679.853</v>
       </c>
       <c r="G84">
         <v>9.359999999999999</v>
@@ -8175,37 +8175,37 @@
         <v>57.5</v>
       </c>
       <c r="M84">
-        <v>158.3778996</v>
+        <v>160.3093374</v>
       </c>
       <c r="N84">
-        <v>-100.8778996</v>
+        <v>-102.8093374</v>
       </c>
       <c r="O84">
-        <v>-26.732643394</v>
+        <v>-27.244474411</v>
       </c>
       <c r="P84">
-        <v>-74.14525620599998</v>
+        <v>-75.56486298900001</v>
       </c>
       <c r="Q84">
-        <v>-65.14525620599998</v>
+        <v>-66.56486298900001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1625727501767415</v>
+        <v>0.1694417354812557</v>
       </c>
       <c r="T84">
-        <v>2.69683025812336</v>
+        <v>2.855467332130617</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09620976183219949</v>
+        <v>0.09505060807518502</v>
       </c>
       <c r="W84">
-        <v>0.2131137381599674</v>
+        <v>0.2133870666158714</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3630557050271679</v>
+        <v>0.3586815399063585</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2059163603229867</v>
+        <v>0.2078163603229867</v>
       </c>
       <c r="C85">
-        <v>-462.5585801149707</v>
+        <v>-472.7742081972315</v>
       </c>
       <c r="D85">
-        <v>207.9344198850293</v>
+        <v>205.9097918027685</v>
       </c>
       <c r="E85">
-        <v>217.953</v>
+        <v>226.1440000000001</v>
       </c>
       <c r="F85">
-        <v>679.853</v>
+        <v>688.044</v>
       </c>
       <c r="G85">
         <v>9.359999999999999</v>
@@ -8257,37 +8257,37 @@
         <v>57.5</v>
       </c>
       <c r="M85">
-        <v>160.3093374</v>
+        <v>162.2407752</v>
       </c>
       <c r="N85">
-        <v>-102.8093374</v>
+        <v>-104.7407752</v>
       </c>
       <c r="O85">
-        <v>-27.244474411</v>
+        <v>-27.756305428</v>
       </c>
       <c r="P85">
-        <v>-75.56486298900001</v>
+        <v>-76.984469772</v>
       </c>
       <c r="Q85">
-        <v>-66.56486298900001</v>
+        <v>-67.984469772</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1694417354812557</v>
+        <v>0.1771693439488342</v>
       </c>
       <c r="T85">
-        <v>2.855467332130617</v>
+        <v>3.033934040388781</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09505060807518502</v>
+        <v>0.09391905321714711</v>
       </c>
       <c r="W85">
-        <v>0.2133870666158714</v>
+        <v>0.2136538872513967</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3586815399063585</v>
+        <v>0.35441152157414</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2078163603229867</v>
+        <v>0.2097163603229867</v>
       </c>
       <c r="C86">
-        <v>-472.7742081972314</v>
+        <v>-482.9507894376328</v>
       </c>
       <c r="D86">
-        <v>205.9097918027685</v>
+        <v>203.9242105623671</v>
       </c>
       <c r="E86">
-        <v>226.1439999999999</v>
+        <v>234.335</v>
       </c>
       <c r="F86">
-        <v>688.0439999999999</v>
+        <v>696.2349999999999</v>
       </c>
       <c r="G86">
         <v>9.359999999999999</v>
@@ -8339,37 +8339,37 @@
         <v>57.5</v>
       </c>
       <c r="M86">
-        <v>162.2407752</v>
+        <v>164.172213</v>
       </c>
       <c r="N86">
-        <v>-104.7407752</v>
+        <v>-106.672213</v>
       </c>
       <c r="O86">
-        <v>-27.75630542799999</v>
+        <v>-28.26813644499999</v>
       </c>
       <c r="P86">
-        <v>-76.98446977199998</v>
+        <v>-78.40407655499997</v>
       </c>
       <c r="Q86">
-        <v>-67.98446977199998</v>
+        <v>-69.40407655499997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1771693439488342</v>
+        <v>0.1859273002120898</v>
       </c>
       <c r="T86">
-        <v>3.033934040388779</v>
+        <v>3.236196309748031</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09391905321714712</v>
+        <v>0.09281412317929832</v>
       </c>
       <c r="W86">
-        <v>0.2136538872513967</v>
+        <v>0.2139144297543215</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.35441152157414</v>
+        <v>0.3502419742615032</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2097163603229867</v>
+        <v>0.2116163603229867</v>
       </c>
       <c r="C87">
-        <v>-482.9507894376328</v>
+        <v>-493.0894426298576</v>
       </c>
       <c r="D87">
-        <v>203.9242105623671</v>
+        <v>201.9765573701424</v>
       </c>
       <c r="E87">
-        <v>234.335</v>
+        <v>242.526</v>
       </c>
       <c r="F87">
-        <v>696.2349999999999</v>
+        <v>704.4259999999999</v>
       </c>
       <c r="G87">
         <v>9.359999999999999</v>
@@ -8421,37 +8421,37 @@
         <v>57.5</v>
       </c>
       <c r="M87">
-        <v>164.172213</v>
+        <v>166.1036508</v>
       </c>
       <c r="N87">
-        <v>-106.672213</v>
+        <v>-108.6036508</v>
       </c>
       <c r="O87">
-        <v>-28.26813644499999</v>
+        <v>-28.779967462</v>
       </c>
       <c r="P87">
-        <v>-78.40407655499997</v>
+        <v>-79.823683338</v>
       </c>
       <c r="Q87">
-        <v>-69.40407655499997</v>
+        <v>-70.823683338</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1859273002120898</v>
+        <v>0.1959363930843819</v>
       </c>
       <c r="T87">
-        <v>3.236196309748031</v>
+        <v>3.467353189015748</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09281412317929832</v>
+        <v>0.09173488918884136</v>
       </c>
       <c r="W87">
-        <v>0.2139144297543215</v>
+        <v>0.2141689131292712</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3502419742615032</v>
+        <v>0.346169393165439</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2116163603229867</v>
+        <v>0.2135163603229867</v>
       </c>
       <c r="C88">
-        <v>-493.0894426298576</v>
+        <v>-503.1912442301455</v>
       </c>
       <c r="D88">
-        <v>201.9765573701424</v>
+        <v>200.0657557698545</v>
       </c>
       <c r="E88">
-        <v>242.526</v>
+        <v>250.717</v>
       </c>
       <c r="F88">
-        <v>704.4259999999999</v>
+        <v>712.617</v>
       </c>
       <c r="G88">
         <v>9.359999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>57.5</v>
       </c>
       <c r="M88">
-        <v>166.1036508</v>
+        <v>168.0350886</v>
       </c>
       <c r="N88">
-        <v>-108.6036508</v>
+        <v>-110.5350886</v>
       </c>
       <c r="O88">
-        <v>-28.779967462</v>
+        <v>-29.291798479</v>
       </c>
       <c r="P88">
-        <v>-79.823683338</v>
+        <v>-81.243290121</v>
       </c>
       <c r="Q88">
-        <v>-70.823683338</v>
+        <v>-72.243290121</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1959363930843819</v>
+        <v>0.2074853463985651</v>
       </c>
       <c r="T88">
-        <v>3.467353189015748</v>
+        <v>3.734072665093882</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09173488918884136</v>
+        <v>0.09068046517517653</v>
       </c>
       <c r="W88">
-        <v>0.2141689131292712</v>
+        <v>0.2144175463116934</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.346169393165439</v>
+        <v>0.3421904346233076</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2135163603229867</v>
+        <v>0.2154163603229867</v>
       </c>
       <c r="C89">
-        <v>-503.1912442301455</v>
+        <v>-513.2572303411937</v>
       </c>
       <c r="D89">
-        <v>200.0657557698545</v>
+        <v>198.1907696588063</v>
       </c>
       <c r="E89">
-        <v>250.717</v>
+        <v>258.908</v>
       </c>
       <c r="F89">
-        <v>712.617</v>
+        <v>720.8079999999999</v>
       </c>
       <c r="G89">
         <v>9.359999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>57.5</v>
       </c>
       <c r="M89">
-        <v>168.0350886</v>
+        <v>169.9665264</v>
       </c>
       <c r="N89">
-        <v>-110.5350886</v>
+        <v>-112.4665264</v>
       </c>
       <c r="O89">
-        <v>-29.291798479</v>
+        <v>-29.803629496</v>
       </c>
       <c r="P89">
-        <v>-81.243290121</v>
+        <v>-82.66289690399999</v>
       </c>
       <c r="Q89">
-        <v>-72.243290121</v>
+        <v>-73.66289690399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2074853463985651</v>
+        <v>0.2209591252651122</v>
       </c>
       <c r="T89">
-        <v>3.734072665093882</v>
+        <v>4.045245387185039</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09068046517517653</v>
+        <v>0.08965000534364043</v>
       </c>
       <c r="W89">
-        <v>0.2144175463116934</v>
+        <v>0.2146605287399696</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3421904346233076</v>
+        <v>0.3383019069571337</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2154163603229867</v>
+        <v>0.2173163603229867</v>
       </c>
       <c r="C90">
-        <v>-513.2572303411937</v>
+        <v>-523.2883985855362</v>
       </c>
       <c r="D90">
-        <v>198.1907696588063</v>
+        <v>196.3506014144637</v>
       </c>
       <c r="E90">
-        <v>258.908</v>
+        <v>267.099</v>
       </c>
       <c r="F90">
-        <v>720.8079999999999</v>
+        <v>728.9989999999999</v>
       </c>
       <c r="G90">
         <v>9.359999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>57.5</v>
       </c>
       <c r="M90">
-        <v>169.9665264</v>
+        <v>171.8979642</v>
       </c>
       <c r="N90">
-        <v>-112.4665264</v>
+        <v>-114.3979642</v>
       </c>
       <c r="O90">
-        <v>-29.803629496</v>
+        <v>-30.315460513</v>
       </c>
       <c r="P90">
-        <v>-82.66289690399999</v>
+        <v>-84.08250368699998</v>
       </c>
       <c r="Q90">
-        <v>-73.66289690399999</v>
+        <v>-75.08250368699998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2209591252651122</v>
+        <v>0.2368826821073952</v>
       </c>
       <c r="T90">
-        <v>4.045245387185039</v>
+        <v>4.412994967838225</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08965000534364043</v>
+        <v>0.088642701912813</v>
       </c>
       <c r="W90">
-        <v>0.2146605287399696</v>
+        <v>0.2148980508889587</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3383019069571337</v>
+        <v>0.3345007619351434</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2173163603229867</v>
+        <v>0.2192163603229867</v>
       </c>
       <c r="C91">
-        <v>-523.2883985855362</v>
+        <v>-533.2857098755196</v>
       </c>
       <c r="D91">
-        <v>196.3506014144637</v>
+        <v>194.5442901244803</v>
       </c>
       <c r="E91">
-        <v>267.099</v>
+        <v>275.29</v>
       </c>
       <c r="F91">
-        <v>728.9989999999999</v>
+        <v>737.1899999999999</v>
       </c>
       <c r="G91">
         <v>9.359999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>57.5</v>
       </c>
       <c r="M91">
-        <v>171.8979642</v>
+        <v>173.829402</v>
       </c>
       <c r="N91">
-        <v>-114.3979642</v>
+        <v>-116.329402</v>
       </c>
       <c r="O91">
-        <v>-30.315460513</v>
+        <v>-30.82729153</v>
       </c>
       <c r="P91">
-        <v>-84.08250368699998</v>
+        <v>-85.50211046999999</v>
       </c>
       <c r="Q91">
-        <v>-75.08250368699998</v>
+        <v>-76.50211046999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2368826821073952</v>
+        <v>0.2559909503181347</v>
       </c>
       <c r="T91">
-        <v>4.412994967838225</v>
+        <v>4.854294464622048</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.088642701912813</v>
+        <v>0.08765778300267063</v>
       </c>
       <c r="W91">
-        <v>0.2148980508889587</v>
+        <v>0.2151302947679703</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3345007619351434</v>
+        <v>0.3307840868025307</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2192163603229867</v>
+        <v>0.2211163603229867</v>
       </c>
       <c r="C92">
-        <v>-533.2857098755196</v>
+        <v>-543.2500900864732</v>
       </c>
       <c r="D92">
-        <v>194.5442901244803</v>
+        <v>192.7709099135269</v>
       </c>
       <c r="E92">
-        <v>275.29</v>
+        <v>283.4810000000001</v>
       </c>
       <c r="F92">
-        <v>737.1899999999999</v>
+        <v>745.381</v>
       </c>
       <c r="G92">
         <v>9.359999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>57.5</v>
       </c>
       <c r="M92">
-        <v>173.829402</v>
+        <v>175.7608398</v>
       </c>
       <c r="N92">
-        <v>-116.329402</v>
+        <v>-118.2608398</v>
       </c>
       <c r="O92">
-        <v>-30.82729153</v>
+        <v>-31.33912254700001</v>
       </c>
       <c r="P92">
-        <v>-85.50211046999999</v>
+        <v>-86.92171725300001</v>
       </c>
       <c r="Q92">
-        <v>-76.50211046999999</v>
+        <v>-77.92171725300001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2559909503181347</v>
+        <v>0.279345500353483</v>
       </c>
       <c r="T92">
-        <v>4.854294464622048</v>
+        <v>5.393660516246721</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08765778300267063</v>
+        <v>0.08669451066198194</v>
       </c>
       <c r="W92">
-        <v>0.2151302947679703</v>
+        <v>0.2153574343859047</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3307840868025307</v>
+        <v>0.3271490968376677</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2211163603229867</v>
+        <v>0.2230163603229867</v>
       </c>
       <c r="C93">
-        <v>-543.2500900864732</v>
+        <v>-553.1824316391924</v>
       </c>
       <c r="D93">
-        <v>192.7709099135269</v>
+        <v>191.0295683608076</v>
       </c>
       <c r="E93">
-        <v>283.4810000000001</v>
+        <v>291.6720000000001</v>
       </c>
       <c r="F93">
-        <v>745.381</v>
+        <v>753.572</v>
       </c>
       <c r="G93">
         <v>9.359999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>57.5</v>
       </c>
       <c r="M93">
-        <v>175.7608398</v>
+        <v>177.6922776</v>
       </c>
       <c r="N93">
-        <v>-118.2608398</v>
+        <v>-120.1922776</v>
       </c>
       <c r="O93">
-        <v>-31.33912254700001</v>
+        <v>-31.850953564</v>
       </c>
       <c r="P93">
-        <v>-86.92171725300001</v>
+        <v>-88.341324036</v>
       </c>
       <c r="Q93">
-        <v>-77.92171725300001</v>
+        <v>-79.341324036</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.279345500353483</v>
+        <v>0.3085386878976684</v>
       </c>
       <c r="T93">
-        <v>5.393660516246721</v>
+        <v>6.067868080777561</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08669451066198194</v>
+        <v>0.08575217902435171</v>
       </c>
       <c r="W93">
-        <v>0.2153574343859047</v>
+        <v>0.2155796361860579</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3271490968376677</v>
+        <v>0.32359312839378</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2230163603229867</v>
+        <v>0.2249163603229867</v>
       </c>
       <c r="C94">
-        <v>-553.1824316391924</v>
+        <v>-563.0835949974237</v>
       </c>
       <c r="D94">
-        <v>191.0295683608076</v>
+        <v>189.3194050025762</v>
       </c>
       <c r="E94">
-        <v>291.6720000000001</v>
+        <v>299.863</v>
       </c>
       <c r="F94">
-        <v>753.572</v>
+        <v>761.7629999999999</v>
       </c>
       <c r="G94">
         <v>9.359999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>57.5</v>
       </c>
       <c r="M94">
-        <v>177.6922776</v>
+        <v>179.6237154</v>
       </c>
       <c r="N94">
-        <v>-120.1922776</v>
+        <v>-122.1237154</v>
       </c>
       <c r="O94">
-        <v>-31.850953564</v>
+        <v>-32.362784581</v>
       </c>
       <c r="P94">
-        <v>-88.341324036</v>
+        <v>-89.76093081899998</v>
       </c>
       <c r="Q94">
-        <v>-79.341324036</v>
+        <v>-80.76093081899998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3085386878976684</v>
+        <v>0.346072786168764</v>
       </c>
       <c r="T94">
-        <v>6.067868080777561</v>
+        <v>6.9347063780315</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08575217902435171</v>
+        <v>0.08483011258322966</v>
       </c>
       <c r="W94">
-        <v>0.2155796361860579</v>
+        <v>0.2157970594528744</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.32359312839378</v>
+        <v>0.3201136323895458</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2249163603229867</v>
+        <v>0.2268163603229867</v>
       </c>
       <c r="C95">
-        <v>-563.0835949974237</v>
+        <v>-572.9544100856256</v>
       </c>
       <c r="D95">
-        <v>189.3194050025762</v>
+        <v>187.6395899143744</v>
       </c>
       <c r="E95">
-        <v>299.863</v>
+        <v>308.054</v>
       </c>
       <c r="F95">
-        <v>761.7629999999999</v>
+        <v>769.954</v>
       </c>
       <c r="G95">
         <v>9.359999999999999</v>
@@ -9077,37 +9077,37 @@
         <v>57.5</v>
       </c>
       <c r="M95">
-        <v>179.6237154</v>
+        <v>181.5551532</v>
       </c>
       <c r="N95">
-        <v>-122.1237154</v>
+        <v>-124.0551532</v>
       </c>
       <c r="O95">
-        <v>-32.362784581</v>
+        <v>-32.87461559800001</v>
       </c>
       <c r="P95">
-        <v>-89.76093081899998</v>
+        <v>-91.180537602</v>
       </c>
       <c r="Q95">
-        <v>-80.76093081899998</v>
+        <v>-82.180537602</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.346072786168764</v>
+        <v>0.3961182505302248</v>
       </c>
       <c r="T95">
-        <v>6.9347063780315</v>
+        <v>8.090490774370085</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08483011258322966</v>
+        <v>0.08392766457702507</v>
       </c>
       <c r="W95">
-        <v>0.2157970594528744</v>
+        <v>0.2160098566927375</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3201136323895458</v>
+        <v>0.316708168215189</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2268163603229867</v>
+        <v>0.2287163603229867</v>
       </c>
       <c r="C96">
-        <v>-572.9544100856256</v>
+        <v>-582.7956776319137</v>
       </c>
       <c r="D96">
-        <v>187.6395899143744</v>
+        <v>185.9893223680863</v>
       </c>
       <c r="E96">
-        <v>308.054</v>
+        <v>316.2450000000001</v>
       </c>
       <c r="F96">
-        <v>769.954</v>
+        <v>778.145</v>
       </c>
       <c r="G96">
         <v>9.359999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>57.5</v>
       </c>
       <c r="M96">
-        <v>181.5551532</v>
+        <v>183.486591</v>
       </c>
       <c r="N96">
-        <v>-124.0551532</v>
+        <v>-125.986591</v>
       </c>
       <c r="O96">
-        <v>-32.87461559800001</v>
+        <v>-33.386446615</v>
       </c>
       <c r="P96">
-        <v>-91.180537602</v>
+        <v>-92.60014438499999</v>
       </c>
       <c r="Q96">
-        <v>-82.180537602</v>
+        <v>-83.60014438499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3961182505302248</v>
+        <v>0.4661819006362699</v>
       </c>
       <c r="T96">
-        <v>8.090490774370085</v>
+        <v>9.708588929244106</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08392766457702507</v>
+        <v>0.08304421547621429</v>
       </c>
       <c r="W96">
-        <v>0.2160098566927375</v>
+        <v>0.2162181739907087</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.316708168215189</v>
+        <v>0.3133743980234501</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2287163603229867</v>
+        <v>0.2306163603229867</v>
       </c>
       <c r="C97">
-        <v>-582.7956776319137</v>
+        <v>-592.6081704407611</v>
       </c>
       <c r="D97">
-        <v>185.9893223680863</v>
+        <v>184.3678295592389</v>
       </c>
       <c r="E97">
-        <v>316.2450000000001</v>
+        <v>324.4360000000001</v>
       </c>
       <c r="F97">
-        <v>778.145</v>
+        <v>786.336</v>
       </c>
       <c r="G97">
         <v>9.359999999999999</v>
@@ -9241,37 +9241,37 @@
         <v>57.5</v>
       </c>
       <c r="M97">
-        <v>183.486591</v>
+        <v>185.4180288</v>
       </c>
       <c r="N97">
-        <v>-125.986591</v>
+        <v>-127.9180288</v>
       </c>
       <c r="O97">
-        <v>-33.386446615</v>
+        <v>-33.898277632</v>
       </c>
       <c r="P97">
-        <v>-92.60014438499999</v>
+        <v>-94.019751168</v>
       </c>
       <c r="Q97">
-        <v>-83.60014438499999</v>
+        <v>-85.019751168</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4661819006362699</v>
+        <v>0.5712773757953374</v>
       </c>
       <c r="T97">
-        <v>9.708588929244106</v>
+        <v>12.13573616155514</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08304421547621429</v>
+        <v>0.08217917156500372</v>
       </c>
       <c r="W97">
-        <v>0.2162181739907087</v>
+        <v>0.2164221513449721</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3133743980234501</v>
+        <v>0.3101100813773725</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2306163603229867</v>
+        <v>0.2325163603229867</v>
       </c>
       <c r="C98">
-        <v>-592.6081704407608</v>
+        <v>-602.3926345996961</v>
       </c>
       <c r="D98">
-        <v>184.3678295592391</v>
+        <v>182.7743654003038</v>
       </c>
       <c r="E98">
-        <v>324.436</v>
+        <v>332.627</v>
       </c>
       <c r="F98">
-        <v>786.3359999999999</v>
+        <v>794.5269999999999</v>
       </c>
       <c r="G98">
         <v>9.359999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>57.5</v>
       </c>
       <c r="M98">
-        <v>185.4180288</v>
+        <v>187.3494666</v>
       </c>
       <c r="N98">
-        <v>-127.9180288</v>
+        <v>-129.8494666</v>
       </c>
       <c r="O98">
-        <v>-33.898277632</v>
+        <v>-34.410108649</v>
       </c>
       <c r="P98">
-        <v>-94.01975116799997</v>
+        <v>-95.43935795100001</v>
       </c>
       <c r="Q98">
-        <v>-85.01975116799997</v>
+        <v>-86.43935795100001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5712773757953361</v>
+        <v>0.7464365010604482</v>
       </c>
       <c r="T98">
-        <v>12.13573616155511</v>
+        <v>16.18098154874014</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08217917156500373</v>
+        <v>0.08133196361072532</v>
       </c>
       <c r="W98">
-        <v>0.2164221513449721</v>
+        <v>0.216621922980591</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3101100813773725</v>
+        <v>0.3069130702291522</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2325163603229867</v>
+        <v>0.2344163603229867</v>
       </c>
       <c r="C99">
-        <v>-602.3926345996961</v>
+        <v>-612.1497906239649</v>
       </c>
       <c r="D99">
-        <v>182.7743654003038</v>
+        <v>181.208209376035</v>
       </c>
       <c r="E99">
-        <v>332.627</v>
+        <v>340.8179999999999</v>
       </c>
       <c r="F99">
-        <v>794.5269999999999</v>
+        <v>802.7179999999998</v>
       </c>
       <c r="G99">
         <v>9.359999999999999</v>
@@ -9405,37 +9405,37 @@
         <v>57.5</v>
       </c>
       <c r="M99">
-        <v>187.3494666</v>
+        <v>189.2809044</v>
       </c>
       <c r="N99">
-        <v>-129.8494666</v>
+        <v>-131.7809044</v>
       </c>
       <c r="O99">
-        <v>-34.410108649</v>
+        <v>-34.92193966599999</v>
       </c>
       <c r="P99">
-        <v>-95.43935795100001</v>
+        <v>-96.85896473399998</v>
       </c>
       <c r="Q99">
-        <v>-86.43935795100001</v>
+        <v>-87.85896473399998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7464365010604482</v>
+        <v>1.096754751590672</v>
       </c>
       <c r="T99">
-        <v>16.18098154874014</v>
+        <v>24.27147232311021</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08133196361072532</v>
+        <v>0.08050204561469752</v>
       </c>
       <c r="W99">
-        <v>0.216621922980591</v>
+        <v>0.2168176176440543</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3069130702291522</v>
+        <v>0.3037813042064058</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2344163603229867</v>
+        <v>0.2363163603229867</v>
       </c>
       <c r="C100">
-        <v>-612.1497906239649</v>
+        <v>-621.8803345428387</v>
       </c>
       <c r="D100">
-        <v>181.208209376035</v>
+        <v>179.6686654571612</v>
       </c>
       <c r="E100">
-        <v>340.8179999999999</v>
+        <v>349.009</v>
       </c>
       <c r="F100">
-        <v>802.7179999999998</v>
+        <v>810.9089999999999</v>
       </c>
       <c r="G100">
         <v>9.359999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>57.5</v>
       </c>
       <c r="M100">
-        <v>189.2809044</v>
+        <v>191.2123422</v>
       </c>
       <c r="N100">
-        <v>-131.7809044</v>
+        <v>-133.7123422</v>
       </c>
       <c r="O100">
-        <v>-34.92193966599999</v>
+        <v>-35.43377068299999</v>
       </c>
       <c r="P100">
-        <v>-96.85896473399998</v>
+        <v>-98.27857151699997</v>
       </c>
       <c r="Q100">
-        <v>-87.85896473399998</v>
+        <v>-89.27857151699997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.096754751590672</v>
+        <v>2.147709503181344</v>
       </c>
       <c r="T100">
-        <v>24.27147232311021</v>
+        <v>48.54294464622043</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08050204561469752</v>
+        <v>0.07968889363879149</v>
       </c>
       <c r="W100">
-        <v>0.2168176176440543</v>
+        <v>0.217009358879973</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3037813042064058</v>
+        <v>0.3007128061841189</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2363163603229867</v>
-      </c>
-      <c r="C101">
-        <v>-621.8803345428387</v>
-      </c>
-      <c r="D101">
-        <v>179.6686654571612</v>
-      </c>
-      <c r="E101">
-        <v>349.009</v>
-      </c>
-      <c r="F101">
-        <v>810.9089999999999</v>
-      </c>
-      <c r="G101">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="H101">
-        <v>357.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>66.5</v>
-      </c>
-      <c r="K101">
-        <v>9</v>
-      </c>
-      <c r="L101">
-        <v>57.5</v>
-      </c>
-      <c r="M101">
-        <v>191.2123422</v>
-      </c>
-      <c r="N101">
-        <v>-133.7123422</v>
-      </c>
-      <c r="O101">
-        <v>-35.43377068299999</v>
-      </c>
-      <c r="P101">
-        <v>-98.27857151699997</v>
-      </c>
-      <c r="Q101">
-        <v>-89.27857151699997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.147709503181344</v>
-      </c>
-      <c r="T101">
-        <v>48.54294464622043</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07968889363879149</v>
-      </c>
-      <c r="W101">
-        <v>0.217009358879973</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3007128061841189</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
